--- a/data_extactor/batch_10_fa/batch_0014_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0014_fa.xlsx
@@ -503,32 +503,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Ademero Content Central | Adobe Acrobat | Adobe Dreamweaver | Adobe InDesign | Adobe Photoshop | Advanced Processing and Imaging OptiView ECM | Alfresco Software Alfresco | Apache Groovy | Apache Tomcat | Apple Final Cut Pro | Autodesk AutoCAD | Autonomy iManage WorkSite | نرم‌افزار مدیریت فرآیند کسب‌وکار BPM | CAPSYS Capture | Cabinet NG CNG-SAFE | Central Desktop | Computhink ViewWise | Conarc iChannel | DB Tech RAS | Dassault Systemes SolidWorks | Day Software CQ5 Web Content Management | Doc.It DM | DocuSign eSignature | نرم‌افزار تصویربرداری اسناد | نرم‌افزار نمایه سازی اسناد | نرم‌افزار سیستم مدیریت اسناد | EMC Captiva | EMC Document Sciences xPression | EMC Documentum | نرم‌افزار مدیریت گزارش‌های سازمانی ERM | Ever Team EverSuite Content Management | زبان نشانه‌گذاری گسترش‌پذیر XML | Fabasoft Folio | نرم‌افزار فشرده‌سازی فایل | نرم‌افزار سیستم فایل | FileHold Systems FileHold | FileMaker Pro | FileVision | Google Ads | Google Analytics | Google Meet | Google Sites | Hewlett Packard Exstream Dialogue | Hyland Software OnBase | زبان نشانه‌گذاری ابرمتن HTML | IBM BPM Blueprint | IBM DB2 | IBM FileNet Content Manager | IBM MVS | IBM Notes | IBM WebSphere MQ | Laserfiche Rio | Linux | Microsoft .NET Framework | Microsoft Access | Microsoft Dynamics | Microsoft Excel | Microsoft Office Document Imaging | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Windows | Microsoft Word | Newgen Software Technologies OmniDocs | Objectif Lune PlanetPress Suite | Objective Electronic Document Management | Office Gemini Diamond Vision | Open Text Web Solutions | OpenDocMan | نرم‌افزار تشخیص نوری کاراکتر OCR | Oracle Java | Oracle PeopleSoft Financials | Oracle SQL Developer | Oracle Universal Content Management | Oracle WebLogic Server | PTC Creo Parametric | Pegasystems SmartBPM | Perceptive Software ImageNow | Perl | Personable Workflow DMS | نرم‌افزار مدیریت سوابق | SAP Business Objects | SAP BusinessObjects Data Integrator | SAP DMS | SAP ERP Financials | SAP PowerBuilder | Saperion ECM | Skype | Systemware | Teradata Database | Thomson Reuters FileCabinet CS | Thomson Reuters GoFileRoom | Treeno Software Treeno Content Server | UNIX | زبان مدل‌سازی یکپارچه UML | نرم‌افزار کنترل نسخه | Vertafore ImageRight | WeVideo | Westbrook Fortis | Xerox DocuShare | Xythos Enterprise Document Management Suite</t>
+          <t>Ademero Content Central | Adobe Acrobat | Adobe Dreamweaver | Adobe InDesign | Adobe Photoshop | Advanced Processing and Imaging OptiView ECM | Alfresco Software Alfresco | Apache Groovy | Apache Tomcat | Apple Final Cut Pro | Autodesk AutoCAD | Autonomy iManage WorkSite | نرم‌افزار مدیریت فرآیند کسب‌وکار BPM | CAPSYS Capture | Cabinet NG CNG-SAFE | Central Desktop | Computhink ViewWise | Conarc iChannel | DB Tech RAS | Dassault Systemes SolidWorks | Day Software CQ5 Web Content Management | Doc.It DM | DocuSign eSignature | نرم‌افزار تصویربرداری اسناد | نرم‌افزار نمایه سازی اسناد | نرم‌افزار سیستم مدیریت اسناد | EMC Captiva | EMC Document Sciences xPression | EMC Documentum | نرم‌افزار مدیریت گزارش‌های سازمانی ERM | Ever Team EverSuite Content Management | زبان نشانه‌گذاری توسعه‌پذیر XML | Fabasoft Folio | نرم‌افزار فشرده‌سازی فایل | نرم‌افزار سیستم فایل | FileHold Systems FileHold | FileMaker Pro | FileVision | Google Ads | Google Analytics | Google Meet | Google Sites | Hewlett Packard Exstream Dialogue | Hyland Software OnBase | زبان نشانه‌گذاری ابرمتن HTML | IBM BPM Blueprint | IBM DB2 | IBM FileNet Content Manager | IBM MVS | IBM Notes | IBM WebSphere MQ | Laserfiche Rio | Linux | Microsoft .NET Framework | Microsoft Access | Microsoft Dynamics | Microsoft Excel | Microsoft Office Document Imaging | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Windows | Microsoft Word | Newgen Software Technologies OmniDocs | Objectif Lune PlanetPress Suite | Objective Electronic Document Management | Office Gemini Diamond Vision | Open Text Web Solutions | OpenDocMan | نرم‌افزار تشخیص نوری کاراکتر OCR | Oracle Java | Oracle PeopleSoft Financials | Oracle SQL Developer | Oracle Universal Content Management | Oracle WebLogic Server | PTC Creo Parametric | Pegasystems SmartBPM | Perceptive Software ImageNow | Perl | Personable Workflow DMS | نرم‌افزار مدیریت سوابق | SAP Business Objects | SAP BusinessObjects Data Integrator | SAP DMS | SAP ERP Financials | SAP PowerBuilder | Saperion ECM | Skype | Systemware | Teradata Database | Thomson Reuters FileCabinet CS | Thomson Reuters GoFileRoom | Treeno Software Treeno Content Server | UNIX | زبان مدل‌سازی یکپارچه UML | نرم‌افزار کنترل نسخه | Vertafore ImageRight | WeVideo | Westbrook Fortis | Xerox DocuShare | Xythos Enterprise Document Management Suite</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | نگارش | تفکر انتقادی | پایش | یادگیری فعال | سخن گفتن | راهبردهای یادگیری</t>
+          <t>درک مطلب | گوش دادن فعال | نگارش | تفکر انتقادی | نظارت | یادگیری فعال | سخن گفتن | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | مدیریت و سازماندهی | رایانه و الکترونیک | خدمات مشتریان و پرسنل | امور اداری | قانون و دولت | آموزش و پرورش</t>
+          <t>زبان انگلیسی | مدیریت و اداره | رایانه و الکترونیک | خدمات مشتری و شخصی | اداری | قانون و دولت | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | سازماندهی اطلاعات | استدلال استنتاجی | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | تشخیص گفتار | انعطاف‌پذیری بستار | روانی ایده‌ها | وضوح گفتار | توجه انتخابی | اصالت</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | ترتیب‌دهی اطلاعات | استدلال قیاسی | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | تشخیص گفتار | انعطاف‌پذیری بستار | روانی ایده‌ها | وضوح گفتار | توجه انتخابی | اصالت</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان به صورت نشسته | اهمیت دقیق یا منظم بودن | نامه‌ها و یادداشت‌های کتبی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | ارتباط با دیگران | محیط داخلی، کنترل‌شده از نظر دما | فشار زمانی | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای نشستن | اهمیت دقیق یا درست بودن | نامه‌ها و یادداشت‌های کتبی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | فشار زمانی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | تحلیلگران هوش تجاری | مدیران داده‌های بالینی | مدیران انطباق | تحلیلگران سیستم‌های رایانه‌ای | مدیران سیستم‌های رایانه‌ای و اطلاعاتی | کاربران ورود داده | متخصصان انبارش داده | مدیران پایگاه داده | معماران پایگاه داده | بایگانان پرونده | فن‌آوران اطلاعات سلامت و ثبت‌کنندگان پزشکی | تحلیلگران امنیت اطلاعات | تحلیلگران مدیریت | متخصصان سوابق پزشکی | کارمندان دفتری عمومی | توسعه‌دهندگان نرم‌افزار | دستیاران آماری | نویسندگان فنی | مدیران وب</t>
+          <t>مدیران خدمات اداری | تحلیلگران هوش تجاری | مدیران داده‌های بالینی | مدیران انطباق | تحلیلگران سیستم‌های کامپیوتری | مدیران کامپیوتر و سیستم‌های اطلاعاتی | اپراتورهای ورود داده | متخصصان انبارش داده | مدیران پایگاه داده | معماران پایگاه داده | کارمندان بایگانی | فن‌آوران اطلاعات سلامت و ثبت‌کنندگان پزشکی | تحلیل‌گران امنیت اطلاعات | تحلیل‌گران مدیریت | متخصصان مدارک پزشکی | کارمندان دفتری عمومی | توسعه‌دهندگان نرم‌افزار | دستیاران آماری | نویسندگان فنی | مدیران وب</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Penetration Testers</t>
+          <t>کارشناسان آزمون نفوذ (Penetration Testers)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -560,32 +560,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Amazon Web Services AWS software | Ansible software | Apple iOS | Apple macOS | Bash | C | C# | C++ | سیستم‌های مدیریت پایگاه داده | Docker | نرم‌افزار فایروال | Ghidra | GitHub | Go | Google Android | Google Cloud software | HP WebInspect | Hex-Rays IDA Pro | IBM Middleware | IBM QRadar SIEM | IBM Terraform | Invicti Acunetix | JavaScript | Kali Linux | Kubernetes | Linux | MITRE ATT&amp;CK software | Magellan Firmware | سیستم‌های اطلاعات مدیریت MIS | Metasploit | Microsoft Active Directory | Microsoft Active Server Pages ASP | Microsoft Azure DevOps Services | Microsoft Azure software | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerShell | Microsoft SQL Server | Microsoft Visual Basic Scripting Edition VBScript | Nmap | Objective C | Oracle Java | Oracle Java 2 Platform Enterprise Edition J2EE | PHP | Perl | Portswigger BurP Suite | Python | Qualys Cloud Platform | RESTful API | Rapid7 Nexpose | Rapid7 software | Ruby | زبان برنامه‌نویسی Rust | زبان نشانه‌گذاری تایید امنیت SAML | ServiceNow | Shell script | ابزارهای توسعه نرم‌افزار | کتابخانه‌های نرم‌افزاری | Splunk Enterprise | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار تست سیستم | Tenable Nessus | UNIX | Vector 35 Binary Ninja | نرم‌افزار برنامه‌های کاربردی وب | نرم‌افزار وب سرور | Wireshark</t>
+          <t>نرم‌افزار Amazon Web Services AWS | نرم‌افزار Ansible | Apple iOS | Apple macOS | Bash | C | C# | C++ | سیستم‌های مدیریت پایگاه داده | Docker | نرم‌افزار فایروال | Ghidra | GitHub | Go | Google Android | نرم‌افزار Google Cloud | HP WebInspect | Hex-Rays IDA Pro | IBM Middleware | IBM QRadar SIEM | IBM Terraform | Invicti Acunetix | JavaScript | Kali Linux | Kubernetes | Linux | نرم‌افزار MITRE ATT&amp;CK | Magellan Firmware | سیستم‌های اطلاعات مدیریت MIS | Metasploit | Microsoft Active Directory | Microsoft Active Server Pages ASP | Microsoft Azure DevOps Services | نرم‌افزار Microsoft Azure | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerShell | Microsoft SQL Server | Microsoft Visual Basic Scripting Edition VBScript | Nmap | Objective C | Oracle Java | Oracle Java 2 Platform Enterprise Edition J2EE | PHP | Perl | Portswigger BurP Suite | Python | Qualys Cloud Platform | RESTful API | Rapid7 Nexpose | Rapid7 software | Ruby | زبان برنامه‌نویسی Rust | زبان نشانه‌گذاری تایید امنیت SAML | ServiceNow | Shell script | ابزارهای توسعه نرم‌افزار | کتابخانه‌های نرم‌افزاری | Splunk Enterprise | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار تست سیستم | Tenable Nessus | UNIX | Vector 35 Binary Ninja | نرم‌افزار برنامه‌های کاربردی وب | نرم‌افزار وب سرور | Wireshark</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | پایش | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | مخابرات | زبان انگلیسی | ریاضیات | مهندسی و فناوری | قانون و دولت | ایمنی و امنیت عمومی | مدیریت و سازماندهی</t>
+          <t>رایانه و الکترونیک | مخابرات | زبان انگلیسی | ریاضیات | مهندسی و فناوری | قانون و دولت | ایمنی و امنیت عمومی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال استنتاجی | استدلال استقرایی | سازماندهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | اشتراک زمانی | تجسم | حفظ کردن | استدلال ریاضی | سهولت در کار با اعداد | سرعت ادراکی | انعطاف‌پذیری بستار</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن | استدلال ریاضی | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، کنترل‌شده از نظر دما | صرف زمان به صورت نشسته | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا منظم بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | تناوب تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | سروکار داشتن با مشتریان خارجی یا عموم مردم به صورت عمومی | اهمیت تکرار وظایف یکسان | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | پیامد خطا</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | اهمیت تکرار وظایف یکسان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامد خطا</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مهندسان بلاک‌چین | معماران شبکه رایانه‌ای | متخصصان پشتیبانی شبکه رایانه‌ای | تحلیلگران سیستم‌های رایانه‌ای | مهندسان/معماران سیستم‌های رایانه‌ای | مدیران سیستم‌های رایانه‌ای و اطلاعاتی | مدیران پایگاه داده | معماران پایگاه داده | تحلیلگران جرم‌یابی دیجیتال | مهندسان ایمنی و بهداشت، به جز مهندسان و بازرسان ایمنی معدن | تحلیلگران امنیت اطلاعات | مهندسان امنیت اطلاعات | تحلیلگران اطلاعاتی | مدیران شبکه و سیستم‌های رایانه‌ای | تحلیلگران کنترل کیفیت | متخصصان مدیریت امنیت | مدیران امنیت | توسعه‌دهندگان نرم‌افزار | تحلیلگران و تست‌کنندگان تضمین کیفیت نرم‌افزار | مهندسان اعتبارسنجی</t>
+          <t>مهندسان بلاک‌چین | معماران شبکه کامپیوتری | متخصصان پشتیبانی شبکه کامپیوتری | تحلیلگران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | مدیران کامپیوتر و سیستم‌های اطلاعاتی | مدیران پایگاه داده | معماران پایگاه داده | تحلیل‌گران جرم‌شناسی دیجیتال | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | تحلیلگران اطلاعاتی | مدیران شبکه و سیستم‌های کامپیوتری | تحلیل‌گران کنترل کیفیت | متخصصان مدیریت امنیت | مدیران امنیتی | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و تست‌کنندگان تضمین کیفیت نرم‌افزار | مهندسان اعتبارسنجی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Information Security Engineers</t>
+          <t>مهندسان امنیت اطلاعات (Information Security Engineers)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -617,32 +617,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>نرم‌افزار اکتیو دایرکتوری | Amazon Web Services AWS CloudFormation | Amazon Web Services AWS software | Ansible software | Apple iOS | Apple macOS | ArcSight Enterprise Threat and Risk Management | Atlassian Confluence | Atlassian JIRA | Bash | پروتکل دروازه مرزی BGP | C | C# | C++ | Chef | نرم‌افزار ویرایش مشارکتی | Docker | Elasticsearch | نرم‌افزار یکپارچه‌سازی برنامه‌های کاربردی سازمانی EAI | نرم‌افزار فایروال | سیستم‌های اطلاعات جغرافیایی GIS | Git | GitHub | Go | Google Cloud software | IBM DB2 | IBM Middleware | IBM QRadar SIEM | IBM Resource Access Control Facility RACF | IBM Terraform | IBM Tivoli software | سیستم تشخیص نفوذ IDS | JavaScript | نشانه‌گذاری شیء جاوااسکریپت JSON | Jenkins CI | Kubernetes | Linux | سیستم‌های اطلاعات مدیریت MIS | McAfee Enterprise Security Manager | Microsoft Access | Microsoft Active Directory | Microsoft Azure Sentinel | Microsoft Azure software | Microsoft Defender Antivirus | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft PowerShell | Microsoft SQL Server | Microsoft SQL Server Integration Services SSIS | Microsoft SQL Server Reporting Services SSRS | Microsoft Security Esssentials | Microsoft SharePoint | Microsoft Teams | Microsoft Visio | Microsoft Windows | Microsoft Windows Server | MongoDB | نرم‌افزار خدمات دایرکتوری شبکه | NoSQL | Oracle Java | Oracle Unified Directory | PHP | Perl | پلتفرم به عنوان سرویس PaaS | Puppet | Python | R | RESTful API | React | Red Hat Enterprise Linux | نرم‌افزار گزارش‌دهی | Ruby | زبان نشانه‌گذاری تایید امنیت SAML | ServiceNow | Shell script | ورود یکباره SSO | Snort | کتابخانه‌های نرم‌افزاری | Splunk Enterprise | زبان پرس‌وجوی ساختاریافته SQL | Tanium software | Tcpdump | Tenable Nessus | UNIX | UNIX Shell | Ubuntu | نرم‌افزار برنامه‌های کاربردی وب | Wireshark</t>
+          <t>نرم‌افزار اکتیو دایرکتوری | Amazon Web Services AWS CloudFormation | نرم‌افزار Amazon Web Services AWS | نرم‌افزار Ansible | Apple iOS | Apple macOS | ArcSight Enterprise Threat and Risk Management | Atlassian Confluence | Atlassian JIRA | Bash | پروتکل مسیریابی مرزی BGP | C | C# | C++ | Chef | نرم‌افزار ویرایش مشارکتی | Docker | Elasticsearch | نرم‌افزار یکپارچه‌سازی برنامه‌های کاربردی سازمانی EAI | نرم‌افزار فایروال | سیستم‌های سیستم اطلاعات جغرافیایی GIS | Git | GitHub | Go | نرم‌افزار Google Cloud | IBM DB2 | IBM Middleware | IBM QRadar SIEM | IBM Resource Access Control Facility RACF | IBM Terraform | نرم‌افزار IBM Tivoli | سیستم تشخیص نفوذ IDS | JavaScript | JavaScript Object Notation JSON | Jenkins CI | Kubernetes | Linux | سیستم‌های اطلاعات مدیریت MIS | McAfee Enterprise Security Manager | Microsoft Access | Microsoft Active Directory | Microsoft Azure Sentinel | نرم‌افزار Microsoft Azure | Microsoft Defender Antivirus | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft PowerShell | Microsoft SQL Server | Microsoft SQL Server Integration Services SSIS | Microsoft SQL Server Reporting Services SSRS | Microsoft Security Esssentials | Microsoft SharePoint | Microsoft Teams | Microsoft Visio | Microsoft Windows | Microsoft Windows Server | MongoDB | نرم‌افزار خدمات دایرکتوری شبکه | NoSQL | Oracle Java | Oracle Unified Directory | PHP | Perl | پلتفرم به عنوان سرویس PaaS | Puppet | Python | R | RESTful API | React | Red Hat Enterprise Linux | نرم‌افزار گزارش‌دهی | Ruby | زبان نشانه‌گذاری تایید امنیت SAML | ServiceNow | Shell script | ورود یکباره SSO | Snort | کتابخانه‌های نرم‌افزاری | Splunk Enterprise | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار Tanium | Tcpdump | Tenable Nessus | UNIX | UNIX Shell | Ubuntu | نرم‌افزار برنامه‌های کاربردی وب | Wireshark</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | نگارش | پایش | سخن گفتن | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | نگارش | نظارت | سخن گفتن | یادگیری فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | مهندسی و فناوری | زبان انگلیسی | مخابرات | خدمات مشتریان و پرسنل</t>
+          <t>رایانه و الکترونیک | مهندسی و فناوری | زبان انگلیسی | مخابرات | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال استنتاجی | سازماندهی اطلاعات | تشخیص گفتار | حساسیت به مسئله | بینایی نزدیک | استدلال استقرایی | بیان کتبی | وضوح گفتار | انعطاف‌پذیری بستار | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | ترتیب‌دهی اطلاعات | تشخیص گفتار | حساسیت به مسئله | بینایی نزدیک | استدلال استقرایی | بیان کتبی | وضوح گفتار | انعطاف‌پذیری بستار | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ایمیل | صرف زمان به صورت نشسته | محیط داخلی، کنترل‌شده از نظر دما | مکالمات تلفنی | اهمیت دقیق یا منظم بودن | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | آزادی در تصمیم‌گیری | فشار زمانی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | سطح رقابت</t>
+          <t>ایمیل | صرف زمان برای نشستن | محیط داخلی، دارای کنترل شرایط محیطی | مکالمات تلفنی | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | آزادی در تصمیم‌گیری | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سطح رقابت</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مهندسان بلاک‌چین | معماران شبکه رایانه‌ای | متخصصان پشتیبانی شبکه رایانه‌ای | تحلیلگران سیستم‌های رایانه‌ای | مهندسان/معماران سیستم‌های رایانه‌ای | متخصصان پشتیبانی کاربران رایانه | مدیران سیستم‌های رایانه‌ای و اطلاعاتی | مدیران پایگاه داده | معماران پایگاه داده | تحلیلگران جرم‌یابی دیجیتال | تحلیلگران امنیت اطلاعات | تحلیلگران اطلاعاتی | مدیران شبکه و سیستم‌های رایانه‌ای | تست‌کنندگان نفوذ | متخصصان مدیریت امنیت | مدیران امنیت | توسعه‌دهندگان نرم‌افزار | تحلیلگران و تست‌کنندگان تضمین کیفیت نرم‌افزار | متخصصان مهندسی مخابرات | مدیران وب</t>
+          <t>مهندسان بلاک‌چین | معماران شبکه کامپیوتری | متخصصان پشتیبانی شبکه کامپیوتری | تحلیلگران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | متخصصان پشتیبانی کاربران کامپیوتر | مدیران کامپیوتر و سیستم‌های اطلاعاتی | مدیران پایگاه داده | معماران پایگاه داده | تحلیل‌گران جرم‌شناسی دیجیتال | تحلیل‌گران امنیت اطلاعات | تحلیلگران اطلاعاتی | مدیران شبکه و سیستم‌های کامپیوتری | کارشناسان آزمون نفوذ | متخصصان مدیریت امنیت | مدیران امنیتی | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و تست‌کنندگان تضمین کیفیت نرم‌افزار | متخصصان مهندسی مخابرات | مدیران وب</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Digital Forensics Analysts</t>
+          <t>تحلیل‌گران جرم‌شناسی دیجیتال (Digital Forensics Analysts)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -674,32 +674,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AccessData FTK | Amazon Simple Storage Service S3 | Amazon Web Services AWS software | Ansible software | Apple iOS | Apple macOS | Bash | پروتکل دروازه مرزی BGP | C | C# | C++ | Cisco Systems Cisco NetFlow Collection Engine | نرم‌افزار جرم‌یابی رایانه‌ای | نرم‌افزار یکپارچه‌سازی برنامه‌های کاربردی سازمانی EAI | زبان نشانه‌گذاری گسترش‌پذیر XML | نرم‌افزار فایروال | سیستم‌های اطلاعات جغرافیایی GIS | Go | Google Workspace software | نرم‌افزار طراحی رابط کاربری گرافیکی GUI | Guidance Software EnCase Enterprise | زبان نشانه‌گذاری ابرمتن HTML | IBM QRadar SIEM | IBM Terraform | سیستم تشخیص نفوذ IDS | JavaScript | Kali Linux | Kubernetes | Linux | MITRE ATT&amp;CK software | سیستم‌های اطلاعات مدیریت MIS | Metasploit | Microsoft Access | Microsoft Active Directory | Microsoft Azure software | Microsoft Defender Antivirus | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft PowerShell | Microsoft Windows | Microsoft Windows Server | نرم‌افزار خدمات دایرکتوری شبکه | OpenVAS | Oracle Java | PHP | Perl | پلتفرم به عنوان سرویس PaaS | Portswigger BurP Suite | Python | R | Ruby | زبان نشانه‌گذاری تایید امنیت SAML | ServiceNow | ورود یکباره SSO | Slack | Snort | Splunk Enterprise | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار تست سیستم | Tenable Nessus | UNIX | نرم‌افزار وب سرور | Wireshark</t>
+          <t>AccessData FTK | Amazon Simple Storage Service S3 | نرم‌افزار Amazon Web Services AWS | نرم‌افزار Ansible | Apple iOS | Apple macOS | Bash | پروتکل مسیریابی مرزی BGP | C | C# | C++ | Cisco Systems Cisco NetFlow Collection Engine | نرم‌افزار جرم‌یابی کامپیوتری | نرم‌افزار یکپارچه‌سازی برنامه‌های کاربردی سازمانی EAI | زبان نشانه‌گذاری توسعه‌پذیر XML | نرم‌افزار فایروال | سیستم‌های سیستم اطلاعات جغرافیایی GIS | Go | نرم‌افزار Google Workspace | نرم‌افزار طراحی رابط کاربری گرافیکی GUI | Guidance Software EnCase Enterprise | زبان نشانه‌گذاری ابرمتن HTML | IBM QRadar SIEM | IBM Terraform | سیستم تشخیص نفوذ IDS | JavaScript | Kali Linux | Kubernetes | Linux | نرم‌افزار MITRE ATT&amp;CK | سیستم‌های اطلاعات مدیریت MIS | Metasploit | Microsoft Access | Microsoft Active Directory | نرم‌افزار Microsoft Azure | Microsoft Defender Antivirus | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft PowerShell | Microsoft Windows | Microsoft Windows Server | نرم‌افزار خدمات دایرکتوری شبکه | OpenVAS | Oracle Java | PHP | Perl | پلتفرم به عنوان سرویس PaaS | Portswigger BurP Suite | Python | R | Ruby | زبان نشانه‌گذاری تایید امنیت SAML | ServiceNow | ورود یکباره SSO | Slack | Snort | Splunk Enterprise | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار تست سیستم | Tenable Nessus | UNIX | نرم‌افزار وب سرور | Wireshark</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | پایش | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | قانون و دولت | زبان انگلیسی | مخابرات | ایمنی و امنیت عمومی | ریاضیات | مهندسی و فناوری | مدیریت و سازماندهی</t>
+          <t>رایانه و الکترونیک | قانون و دولت | زبان انگلیسی | مخابرات | ایمنی و امنیت عمومی | ریاضیات | مهندسی و فناوری | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال استنتاجی | استدلال استقرایی | سازماندهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | اشتراک زمانی | تجسم | حفظ کردن | استدلال ریاضی | سهولت در کار با اعداد | سرعت ادراکی | انعطاف‌پذیری بستار</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن | استدلال ریاضی | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، کنترل‌شده از نظر دما | صرف زمان به صورت نشسته | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا منظم بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | تناوب تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | سروکار داشتن با مشتریان خارجی یا عموم مردم به صورت عمومی | پیامد خطا | اهمیت تکرار وظایف یکسان</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | پیامد خطا | اهمیت تکرار وظایف یکسان</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>تکنسین‌های بیوانفورماتیک | تحلیلگران هوش تجاری | معماران شبکه رایانه‌ای | متخصصان پشتیبانی شبکه رایانه‌ای | تحلیلگران سیستم‌های رایانه‌ای | مدیران سیستم‌های رایانه‌ای و اطلاعاتی | مدیران پایگاه داده | معماران پایگاه داده | متخصصان مدیریت اسناد | تکنسین‌های علوم جرم‌یابی | آزمایش‌کنندگان، بازرسان و تحلیلگران تقلب | ماموران نظارت بر قمار و بازرسان قمار | فن‌آوران و تکنسین‌های سیستم‌های اطلاعات جغرافیایی | تحلیلگران امنیت اطلاعات | مهندسان امنیت اطلاعات | تحلیلگران اطلاعاتی | تست‌کنندگان نفوذ | ماموران شناسایی و سوابق پلیس | متخصصان مدیریت امنیت | مدیران امنیت</t>
+          <t>تکنسین‌های بیوانفورماتیک | تحلیلگران هوش تجاری | معماران شبکه کامپیوتری | متخصصان پشتیبانی شبکه کامپیوتری | تحلیلگران سیستم‌های کامپیوتری | مدیران کامپیوتر و سیستم‌های اطلاعاتی | مدیران پایگاه داده | معماران پایگاه داده | متخصصان مدیریت اسناد | تکنسین‌های علوم قانونی | بازرسان، محققان و تحلیلگران کلاهبرداری | ماموران نظارت بر قمار و بازرسان قمار | متخصصان و تکنسین‌های سیستم‌های اطلاعات جغرافیایی | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | تحلیلگران اطلاعاتی | کارشناسان آزمون نفوذ | افسران شناسایی و سوابق پلیس | متخصصان مدیریت امنیت | مدیران امنیتی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Blockchain Engineers</t>
+          <t>مهندسان بلاک‌چین (Blockchain Engineers)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -731,32 +731,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Amazon Elastic Container Service ECS | Amazon Kinesis | Amazon Simple Storage Service S3 | Amazon Web Services AWS CloudFormation | Amazon Web Services AWS software | Ansible software | Apache Kafka | Atlassian Confluence | Atlassian JIRA | C | C# | C++ | Docker | نرم‌افزار یکپارچه‌سازی برنامه‌های کاربردی سازمانی EAI | Git | GitHub | Go | Google Angular | Grafana Labs Grafana Cloud | IBM Terraform | JavaScript | Jenkins CI | Kotlin | Kubernetes | Linux | کامپایلرهای ماشین مجازی سطح پایین LLVM | معماری میکروسرویس‌ها | Microsoft Azure software | MongoDB | MySQL | NoSQL | Node.js | Oracle Java | Oracle Java Message Service JMS | PostgreSQL | Python | RESTful API | RabbitMQ | React | زبان برنامه‌نویسی Rust | نرم‌افزار به عنوان سرویس SaaS | کتابخانه‌های نرم‌افزاری | Solidity | نرم‌افزار ویرایشگر کد منبع | Splunk Enterprise | Spring Boot | Spring Framework | زبان پرس‌وجوی ساختاریافته SQL | TypeScript | نرم‌افزار فریم‌ورک وب</t>
+          <t>Amazon Elastic Container Service ECS | Amazon Kinesis | Amazon Simple Storage Service S3 | Amazon Web Services AWS CloudFormation | نرم‌افزار Amazon Web Services AWS | نرم‌افزار Ansible | Apache Kafka | Atlassian Confluence | Atlassian JIRA | C | C# | C++ | Docker | نرم‌افزار یکپارچه‌سازی برنامه‌های کاربردی سازمانی EAI | Git | GitHub | Go | Google Angular | Grafana Labs Grafana Cloud | IBM Terraform | JavaScript | Jenkins CI | Kotlin | Kubernetes | Linux | کامپایلرهای ماشین مجازی سطح پایین LLVM | معماری میکروسرویس‌ها | نرم‌افزار Microsoft Azure | MongoDB | MySQL | NoSQL | Node.js | Oracle Java | سرویس پیام جاوا JMS | PostgreSQL | Python | RESTful API | RabbitMQ | React | زبان برنامه‌نویسی Rust | نرم‌افزار به عنوان سرویس SaaS | کتابخانه‌های نرم‌افزاری | Solidity | نرم‌افزار ویرایشگر کد منبع | Splunk Enterprise | Spring Boot | Spring Framework | زبان پرس‌وجوی ساختاریافته SQL | TypeScript | نرم‌افزار فریم‌ورک وب</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | پایش | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | ریاضیات | زبان انگلیسی | مهندسی و فناوری | مخابرات | اقتصاد و حسابداری | مدیریت و سازماندهی | طراحی</t>
+          <t>رایانه و الکترونیک | ریاضیات | زبان انگلیسی | مهندسی و فناوری | مخابرات | اقتصاد و حسابداری | مدیریت و اداره | طراحی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال استنتاجی | استدلال استقرایی | سازماندهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | اشتراک زمانی | تجسم | حفظ کردن | استدلال ریاضی | سهولت در کار با اعداد | سرعت ادراکی | انعطاف‌پذیری بستار</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن | استدلال ریاضی | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، کنترل‌شده از نظر دما | صرف زمان به صورت نشسته | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا منظم بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | تناوب تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | سروکار داشتن با مشتریان خارجی یا عموم مردم به صورت عمومی | اهمیت تکرار وظایف یکسان | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | درجه خودکارسازی</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | اهمیت تکرار وظایف یکسان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | میزان خودکارسازی</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>تحلیلگران هوش تجاری | مهندسان سخت‌افزار رایانه | معماران شبکه رایانه‌ای | متخصصان پشتیبانی شبکه رایانه‌ای | برنامه‌نویسان رایانه | تحلیلگران سیستم‌های رایانه‌ای | مهندسان/معماران سیستم‌های رایانه‌ای | متخصصان انبارش داده | مدیران پایگاه داده | معماران پایگاه داده | تحلیلگران امنیت اطلاعات | مهندسان امنیت اطلاعات | مهندسان مکاترونیک | مدیران شبکه و سیستم‌های رایانه‌ای | تست‌کنندگان نفوذ | توسعه‌دهندگان نرم‌افزار | تحلیلگران و تست‌کنندگان تضمین کیفیت نرم‌افزار | مدیران وب | توسعه‌دهندگان وب | طراحان رابط‌های دیجیتال و وب</t>
+          <t>تحلیلگران هوش تجاری | مهندسان سخت‌افزار کامپیوتر | معماران شبکه کامپیوتری | متخصصان پشتیبانی شبکه کامپیوتری | برنامه‌نویسان کامپیوتر | تحلیلگران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | متخصصان انبارش داده | مدیران پایگاه داده | معماران پایگاه داده | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | مهندسان مکاترونیک | مدیران شبکه و سیستم‌های کامپیوتری | کارشناسان آزمون نفوذ | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و تست‌کنندگان تضمین کیفیت نرم‌افزار | مدیران وب | توسعه‌دهندگان وب | طراحان رابط دیجیتال و وب</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Computer Systems Engineers/Architects</t>
+          <t>مهندسان و معماران سامانه‌های رایانه‌ای (Computer Systems Engineers/Architects)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -788,32 +788,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3M Post-it App | AJAX | Adobe AIR | Adobe Acrobat | Adobe ActionScript | Adobe Creative Cloud software | Adobe Dreamweaver | Adobe Flex | Adobe FrameMaker | Adobe Photoshop | برنامه‌نویسی پیشرفته برنامه‌های تجاری ABAP | Altia Design | Amazon DynamoDB | Amazon Elastic Compute Cloud EC2 | Amazon Redshift | Amazon Simple Storage Service S3 | Amazon Web Services AWS CloudFormation | Amazon Web Services AWS software | Ansible software | Aonix Software Through Pictures | Apache Airflow | Apache Ant | Apache Cassandra | Apache Groovy | Apache HTTP Server | Apache Hadoop | Apache Hive | Apache Kafka | Apache Maven | Apache Pig | Apache Solr | Apache Spark | Apache Struts | Apache Subversion SVN | Apache Tomcat | Apple Final Cut Pro | Apple macOS | Atlassian Bamboo | Atlassian Bitbucket | Atlassian Confluence | Atlassian JIRA | Autodesk AutoCAD | Autodesk Revit | BEA Tuxedo | Backbone.js | Basecamp | Bash | Bentley MicroStation | Blink | پروتکل دروازه مرزی BGP | Borland VisiBroker | BroadVision software | C | C# | C++ | برگه‌های سبک آبشاری CSS | Chef | Cisco IOS | Cisco Webex | نرم‌افزار رایانش ابری Citrix | Clarity Systems IBM Clarity | زبان مشترک متمایل به تجارت COBOL | نرم‌افزار طراحی و ترسیم به کمک رایانه CADD | سیستم کنترل اطلاعات مشتری CICS | DBTools Software DBManager Professional | Dassault Systemes CATIA | Dassault Systemes SolidWorks | Delphi Technology | Django | Docker | Dropbox | Drupal | زبان نشانه‌گذاری ابرمتن پویا DHTML | نرم‌افزار ESRI ArcGIS | Eclipse IDE | Eko | Elasticsearch | Enterprise JavaBeans | Epic Systems | Ext JS | زبان نشانه‌گذاری ابرمتن گسترش‌پذیر XHTML | زبان نشانه‌گذاری گسترش‌پذیر XML | FileMaker Pro | نرم‌افزار فایروال | ترجمه فرمول/مترجم FORTRAN | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Git | GitHub | GitLab | Go | Google Ads | Google Analytics | Google Angular | Google Cloud software | Grafana Labs Grafana Cloud | Grails | GraphQL | Hewlett Packard HP-UX | Hewlett Packard LoadRunner | Hibernate ORM | نرم‌افزار مدیریت منابع انسانی HRMS | زبان نشانه‌گذاری ابرمتن HTML | IBM AIX | IBM Cognos Impromptu | IBM DB2 | IBM Domino | IBM ILOG | IBM InfoSphere DataStage | IBM Infosphere Information Server | IBM Lotus SameTime | IBM Notes | نرم‌افزار IBM Power Systems | IBM Rational Application Developer | IBM Rational Build Forge | IBM Rational ClearCase | IBM Rational Rose XDE | IBM SPSS Statistics | IBM Terraform | IBM WebSphere | IBM WebSphere MQ | IONA Orbix | InScribe | نرم‌افزار محیط توسعه یکپارچه IDE | سیستم تشخیص نفوذ IDS | JUnit | JavaScript | نشانه‌گذاری شیء جاوااسکریپت JSON | Jenkins CI | زبان کنترل کار JCL | Jupyter Notebook | KornShell | Kubernetes | LAMP Stack | LexisNexis | Linux | نرم‌افزار شبکه محلی LAN | نرم‌افزار MEDITECH | Magellan Firmware | Marketo Marketing Automation | McAfee | MicroStrategy | معماری میکروسرویس‌ها | Microsoft .NET Framework | Microsoft ASP.NET | Microsoft ASP.NET Core MVC | Microsoft Access | Microsoft Active Directory | Microsoft Active Server Pages ASP | Microsoft ActiveX | Microsoft Azure software | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | Microsoft Exchange | Microsoft Internet Information Services (IIS) | نرم‌افزار Microsoft Office | نرم‌افزار Microsoft Power Platform | Microsoft PowerPoint | Microsoft PowerShell | Microsoft Project | Microsoft SQL Server | Microsoft SQL Server Integration Services SSIS | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Teams | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Basic for Applications VBA | Microsoft Visual Studio | Microsoft Windows | Microsoft Windows Server | Minitab | MongoDB | MySQL | Nagios | National Instruments LabVIEW | NetSuite ERP | سیستم‌های پیشگیری از نفوذ شبکه NIPS | NoSQL | Node.js | نرم‌افزار امنیت سایبری NortonLifeLock | Objective C | Oracle Business Intelligence Enterprise Edition | Oracle Cloud software | Oracle Database | Oracle E-Business Suite Financials | Oracle Eloqua | Oracle Fusion Applications | Oracle Fusion Middleware | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle JDBC | Oracle Java | Oracle Java 2 Platform Enterprise Edition J2EE | Oracle JavaServer Pages JSP | Oracle PL/SQL | Oracle PeopleSoft | Oracle Primavera Enterprise Project Portfolio Management | Oracle Solaris | Oracle Taleo | Oracle WebLogic Server | PHP | PTC Creo Parametric | Perforce Helix software | Perl | PostgreSQL | Prometheus | Puppet | Python | Qlik Tech QlikView | Quest Erwin Data Modeler | R | React | Red Hat Enterprise Linux | Red Hat OpenShift | Red Hat WildFly | Redis | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | Ruby | Ruby on Rails | SAP Business Objects | SAP Crystal Reports | نرم‌افزار SAP | SAS | Salesforce Visualforce | Salesforce software | Scala | Selenium | ServiceNow | Shell script | Skype | Slack | Smalltalk | Snort | نرم‌افزار به عنوان سرویس SaaS | Splunk Enterprise | Spring Boot | Spring Framework | StataCorp Stata | نرم‌افزار شبکه ذخیره‌سازی SAN | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار کنترل نظارتی و جمع‌آوری داده SCADA | Swift | Symark PowerBroker | Tableau | Teradata Database | The MathWorks MATLAB | ToadSoft Toad | Transact-SQL | Trimble SketchUp Pro | TypeScript | UNIX | UNIX Shell | Ubuntu | زبان مدل‌سازی یکپارچه UML | VMWare ESX Server | VMware | Verilog | Veritas NetBackup | نرم‌افزار شبکه خصوصی مجازی VPN | نرم‌افزار سیستم انتقال صدا روی پروتکل اینترنت VoIP | نرم‌افزار مرورگر وب | نرم‌افزار شبکه گسترده WAN | Wireshark | jQuery | xQuery</t>
+          <t>3M Post-it App | AJAX | Adobe AIR | Adobe Acrobat | Adobe ActionScript | نرم‌افزار Adobe Creative Cloud | Adobe Dreamweaver | Adobe Flex | Adobe FrameMaker | Adobe Photoshop | برنامه‌نویسی پیشرفته برنامه‌های تجاری ABAP | Altia Design | Amazon DynamoDB | Amazon Elastic Compute Cloud EC2 | Amazon Redshift | Amazon Simple Storage Service S3 | Amazon Web Services AWS CloudFormation | نرم‌افزار Amazon Web Services AWS | نرم‌افزار Ansible | Aonix Software Through Pictures | Apache Airflow | Apache Ant | Apache Cassandra | Apache Groovy | Apache HTTP Server | Apache Hadoop | Apache Hive | Apache Kafka | Apache Maven | Apache Pig | Apache Solr | Apache Spark | Apache Struts | Apache Subversion SVN | Apache Tomcat | Apple Final Cut Pro | Apple macOS | Atlassian Bamboo | Atlassian Bitbucket | Atlassian Confluence | Atlassian JIRA | Autodesk AutoCAD | Autodesk Revit | BEA Tuxedo | Backbone.js | Basecamp | Bash | Bentley MicroStation | Blink | پروتکل مسیریابی مرزی BGP | Borland VisiBroker | BroadVision software | C | C# | C++ | برگه‌های سبک آبشاری CSS | Chef | Cisco IOS | Cisco Webex | نرم‌افزار رایانش ابری Citrix | Clarity Systems IBM Clarity | زبان مشترک تجاری COBOL | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | سیستم کنترل اطلاعات مشتری CICS | DBTools Software DBManager Professional | Dassault Systemes CATIA | Dassault Systemes SolidWorks | Delphi Technology | Django | Docker | Dropbox | Drupal | زبان نشانه‌گذاری ابرمتن پویا DHTML | نرم‌افزار ESRI ArcGIS | Eclipse IDE | Eko | Elasticsearch | Enterprise JavaBeans | Epic Systems | Ext JS | زبان نشانه‌گذاری ابرمتن توسعه‌پذیر XHTML | زبان نشانه‌گذاری توسعه‌پذیر XML | FileMaker Pro | نرم‌افزار فایروال | Formula translation/translator FORTRAN | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Git | GitHub | GitLab | Go | Google Ads | Google Analytics | Google Angular | نرم‌افزار Google Cloud | Grafana Labs Grafana Cloud | Grails | GraphQL | Hewlett Packard HP-UX | Hewlett Packard LoadRunner | Hibernate ORM | نرم‌افزار مدیریت منابع انسانی HRMS | زبان نشانه‌گذاری ابرمتن HTML | IBM AIX | IBM Cognos Impromptu | IBM DB2 | IBM Domino | IBM ILOG | IBM InfoSphere DataStage | IBM Infosphere Information Server | IBM Lotus SameTime | IBM Notes | نرم‌افزار IBM Power Systems | IBM Rational Application Developer | IBM Rational Build Forge | IBM Rational ClearCase | IBM Rational Rose XDE | IBM SPSS Statistics | IBM Terraform | IBM WebSphere | IBM WebSphere MQ | IONA Orbix | InScribe | نرم‌افزار محیط توسعه یکپارچه IDE | سیستم تشخیص نفوذ IDS | JUnit | JavaScript | JavaScript Object Notation JSON | Jenkins CI | زبان کنترل کار JCL | Jupyter Notebook | KornShell | Kubernetes | LAMP Stack | LexisNexis | Linux | نرم‌افزار شبکه محلی LAN | نرم‌افزار MEDITECH | Magellan Firmware | Marketo Marketing Automation | McAfee | MicroStrategy | معماری میکروسرویس‌ها | Microsoft .NET Framework | Microsoft ASP.NET | Microsoft ASP.NET Core MVC | Microsoft Access | Microsoft Active Directory | Microsoft Active Server Pages ASP | Microsoft ActiveX | نرم‌افزار Microsoft Azure | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | Microsoft Exchange | Microsoft Internet Information Services (IIS) | نرم‌افزار Microsoft Office | نرم‌افزار Microsoft Power Platform | Microsoft PowerPoint | Microsoft PowerShell | Microsoft Project | Microsoft SQL Server | Microsoft SQL Server Integration Services SSIS | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Teams | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Basic for Applications VBA | Microsoft Visual Studio | Microsoft Windows | Microsoft Windows Server | Minitab | MongoDB | MySQL | Nagios | National Instruments LabVIEW | NetSuite ERP | سیستم‌های پیشگیری از نفوذ شبکه NIPS | NoSQL | Node.js | نرم‌افزار امنیت سایبری NortonLifeLock | Objective C | Oracle Business Intelligence Enterprise Edition | Oracle Cloud software | Oracle Database | Oracle E-Business Suite Financials | Oracle Eloqua | Oracle Fusion Applications | Oracle Fusion Middleware | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle JDBC | Oracle Java | Oracle Java 2 Platform Enterprise Edition J2EE | Oracle JavaServer Pages JSP | Oracle PL/SQL | Oracle PeopleSoft | Oracle Primavera Enterprise Project Portfolio Management | Oracle Solaris | Oracle Taleo | Oracle WebLogic Server | PHP | PTC Creo Parametric | نرم‌افزار Perforce Helix | Perl | PostgreSQL | Prometheus | Puppet | Python | Qlik Tech QlikView | Quest Erwin Data Modeler | R | React | Red Hat Enterprise Linux | Red Hat OpenShift | Red Hat WildFly | Redis | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | Ruby | Ruby on Rails | SAP Business Objects | SAP Crystal Reports | نرم‌افزار SAP | SAS | Salesforce Visualforce | نرم‌افزار Salesforce | Scala | Selenium | ServiceNow | Shell script | Skype | Slack | Smalltalk | Snort | نرم‌افزار به عنوان سرویس SaaS | Splunk Enterprise | Spring Boot | Spring Framework | StataCorp Stata | نرم‌افزار شبکه ذخیره‌سازی SAN | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | Swift | Symark PowerBroker | Tableau | Teradata Database | The MathWorks MATLAB | ToadSoft Toad | Transact-SQL | Trimble SketchUp Pro | TypeScript | UNIX | UNIX Shell | Ubuntu | زبان مدل‌سازی یکپارچه UML | VMWare ESX Server | VMware | Verilog | Veritas NetBackup | نرم‌افزار شبکه خصوصی مجازی VPN | نرم‌افزار سیستم انتقال صدا روی پروتکل اینترنت VoIP | نرم‌افزار مرورگر وب | نرم‌افزار شبکه گسترده WAN | Wireshark | jQuery | xQuery</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | نگارش | سخن گفتن | یادگیری فعال | پایش | راهبردهای یادگیری | علوم | ریاضیات</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | نگارش | سخن گفتن | یادگیری فعال | نظارت | راهبردهای یادگیری | علوم | ریاضیات</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | زبان انگلیسی | مخابرات | خدمات مشتریان و پرسنل | مهندسی و فناوری | مدیریت و سازماندهی</t>
+          <t>رایانه و الکترونیک | زبان انگلیسی | مخابرات | خدمات مشتری و شخصی | مهندسی و فناوری | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال استنتاجی | استدلال استقرایی | سازماندهی اطلاعات | اصالت | بینایی نزدیک | روانی ایده‌ها | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | سهولت در کار با اعداد | استدلال ریاضی | تشخیص گفتار | توجه انتخابی | سرعت ادراکی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | اصالت | بینایی نزدیک | روانی ایده‌ها | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | توانایی عددی | استدلال ریاضی | تشخیص گفتار | توجه انتخابی | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ایمیل | محیط داخلی، کنترل‌شده از نظر دما | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا منظم بودن | ارتباط با دیگران | تاثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان به صورت نشسته | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | فشار زمانی | اهمیت تکرار وظایف یکسان | سطح رقابت | پیامد خطا | تناوب تصمیم‌گیری</t>
+          <t>ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | ارتباط با دیگران | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای نشستن | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | فشار زمانی | اهمیت تکرار وظایف یکسان | سطح رقابت | پیامد خطا | فراوانی تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مهندسان بلاک‌چین | مهندسان سخت‌افزار رایانه | معماران شبکه رایانه‌ای | متخصصان پشتیبانی شبکه رایانه‌ای | برنامه‌نویسان رایانه | تحلیلگران سیستم‌های رایانه‌ای | متخصصان پشتیبانی کاربران رایانه | مدیران سیستم‌های رایانه‌ای و اطلاعاتی | متخصصان انبارش داده | مدیران پایگاه داده | معماران پایگاه داده | تحلیلگران امنیت اطلاعات | مهندسان امنیت اطلاعات | مدیران شبکه و سیستم‌های رایانه‌ای | تست‌کنندگان نفوذ | متخصصان مدیریت پروژه | توسعه‌دهندگان نرم‌افزار | تحلیلگران و تست‌کنندگان تضمین کیفیت نرم‌افزار | متخصصان مهندسی مخابرات | طراحان رابط‌های دیجیتال و وب</t>
+          <t>مهندسان بلاک‌چین | مهندسان سخت‌افزار کامپیوتر | معماران شبکه کامپیوتری | متخصصان پشتیبانی شبکه کامپیوتری | برنامه‌نویسان کامپیوتر | تحلیلگران سیستم‌های کامپیوتری | متخصصان پشتیبانی کاربران کامپیوتر | مدیران کامپیوتر و سیستم‌های اطلاعاتی | متخصصان انبارش داده | مدیران پایگاه داده | معماران پایگاه داده | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | مدیران شبکه و سیستم‌های کامپیوتری | کارشناسان آزمون نفوذ | متخصصان مدیریت پروژه | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و تست‌کنندگان تضمین کیفیت نرم‌افزار | متخصصان مهندسی مخابرات | طراحان رابط دیجیتال و وب</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Information Technology Project Managers</t>
+          <t>مدیران پروژه فناوری اطلاعات (Information Technology Project Managers)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>24SevenOffice Project | 3M Post-it App | AEC Software FastTrack Schedule | AJAX | AMS REALTIME Projects | Actano Rplan | Adobe Acrobat | Adobe ActionScript | Adobe Creative Cloud software | Adobe Dreamweaver | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | برنامه‌نویسی پیشرفته برنامه‌های تجاری ABAP | Airtable | Amazon DynamoDB | Amazon Elastic Compute Cloud EC2 | Amazon Kinesis | Amazon Redshift | Amazon Web Services AWS software | Ansible software | AnthillPro | Apache Ant | Apache Cassandra | Apache Continuum | Apache Groovy | Apache Gump | Apache HTTP Server | Apache Hadoop | Apache Hive | Apache Kafka | Apache Maven | Apache Pig | Apache Solr | Apache Spark | Apache Struts | Apache Subversion SVN | Apache Tomcat | Apple Final Cut Pro | Apple macOS | Ascensio Systems TeamLab | Assembla | AtTask | Atlassian Bamboo | Atlassian Confluence | Atlassian JIRA | Autodesk AutoCAD | Autodesk Revit | Automation Centre TrackerSuite.Net | Backbone.js | Basecamp | Bash | Blackbaud The Raiser's Edge | Blackboard software | BrightWork pmPoint | C | C# | C++ | CA Technologies CA Clarity PPM for IT Governance | CS Odessa ConceptDraw Project | Canonical Launchpad | برگه‌های سبک آبشاری CSS | Central Desktop | Chef | Cisco IOS | Cisco Webex | نرم‌افزار رایانش ابری Citrix | Clarity Systems IBM Clarity | Clarizen | نرم‌افزار میزبانی کد | نرم‌افزار مدیریت چرخه حیات برنامه مشارکتی ALM | زبان مشترک متمایل به تجارت COBOL | نرم‌افزار یکپارچه‌سازی مداوم | Countersoft Gemini | CruiseControl | سیستم کنترل اطلاعات مشتری CICS | Daptiv PPM | Dassault Systemes CATIA | Delphi Technology | Digital Crew Teamwork Project Manager | Disarea 5pm | Django | Docker | نرم‌افزار سیستم مدیریت اسناد | Drupal | زبان نشانه‌گذاری ابرمتن پویا DHTML | نرم‌افزار ESRI ArcGIS | Eclipse IDE | Edgewell Trac | Edulastic | Elasticsearch | ElectricCloud ElectricCommander | Element Software Copper | Endeavour Agile ALM | Enterprise JavaBeans | Epic Systems | Experience in Software Project KickStart | Ext JS | زبان نشانه‌گذاری ابرمتن گسترش‌پذیر XHTML | زبان نشانه‌گذاری گسترش‌پذیر XML | Facebook | Feng Office Collaboration Platform | FileMaker Pro | FinalBuilder | Fog Creek Software FogBugz | Forum One Communications ProjectSpaces | GanttProject | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Git | GitHub | Glasscubes | Go | Google Ads | Google Analytics | Google Angular | Google Docs | Google Drive | Google Meet | سیستم کدگذاری رویه مشترک مراقبت‌های بهداشتی HCPCS | Hewlett Packard HP Project Portfolio Management Solution | Hewlett Packard HP-UX | Hewlett Packard LoadRunner | Hibernate ORM | نرم‌افزار مدیریت منابع انسانی HRMS | HyperOffice Collaboration Suite | زبان نشانه‌گذاری ابرمتن HTML | IBM Cognos Impromptu | IBM DB2 | IBM Domino | IBM InfoSphere DataStage | IBM Notes | نرم‌افزار IBM Power Systems | IBM Rational Build Forge | IBM SPSS Statistics | IBM Software Configuration and Library Manager SCLM | IBM WebSphere | IBM WebSphere MQ | InLoox | نرم‌افزار محیط توسعه یکپارچه IDE | Intellisys Project Desktop | Intland Software codeBeamer | نرم‌افزار سیستم ردیابی مشکلات | JUnit | JamBoard | JavaScript | نشانه‌گذاری شیء جاوااسکریپت JSON | JetBrains Team City | زبان کنترل کار JCL | Jupyter Notebook | KOffice.org Kplato | Kforge | Kidasa Milestones Professional | KommandCore | KornShell | LAMP Stack | LexisNexis | Linux | LiquidPlanner | LogMeIn GoToMeeting | Logic Software Easy Projects.NET | LuntBuild | MPI Micro Planner X-Pert | Madrigal Soft Tools Delegator | MantisBT | Marketo Marketing Automation | MatchWare MindView | McAfee | MicroStrategy | Microsoft .NET Framework | Microsoft ASP.NET | Microsoft ASP.NET Core MVC | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft ActiveX | Microsoft Azure software | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | Microsoft Exchange | Microsoft Office software | Microsoft OneNote | Microsoft Outlook | Microsoft PowerPoint | Microsoft PowerShell | Microsoft Project | Microsoft Publisher | Microsoft SQL Server | Microsoft SQL Server Integration Services SSIS | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Team Foundation Server | Microsoft Teams | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Basic for Applications VBA | Microsoft Visual Studio | Microsoft Windows | Microsoft Windows Server | Microsoft Word | نرم‌افزار نقشه‌برداری ذهنی | MindGenius | Minitab | MinuteMan Systems MinuteMan Project Management Software | MongoDB | MySQL | Nagios | NetSuite ERP | Ninian Huddle | NoSQL | Node.js | نرم‌افزار امنیت سایبری NortonLifeLock | NovaMind Merlin Project Manager | O3spaces Workplace | Objective C | Objective Decision Contactizer Pro | OfficeWork Software TurboProject | Open Dynamics Collabtive | OpenMake Software Meister | OpenMake Software Mojo | Oracle Business Intelligence Enterprise Edition | Oracle Database | Oracle E-Business Suite Financials | Oracle Eloqua | Oracle Fusion Applications | Oracle Fusion Middleware | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle JDBC | Oracle Java | Oracle Java 2 Platform Enterprise Edition J2EE | Oracle JavaServer Pages JSP | Oracle PL/SQL | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Primavera Enterprise Project Portfolio Management | Oracle Primavera P6 Professional Project Management | Oracle Solaris | Oracle Taleo | Oracle WebLogic Server | PHP | Palbridge Ubidesk | Perforce Helix software | Perl | Planbox | Planisware | Planview Process Builder | PostgreSQL | Project Manager Online ProjectManager.com | نرم‌افزار مدیریت سبد پروژه PPM | Project-Open | Project.net | ProjectLibre | Projecturf | Puppet | Python | QSM SLIM Suite | Qlik Tech QlikView | Quest Erwin Data Modeler | نرم‌افزار مدیریت کسب‌وکار QuickBase | R | React | Red Hat Enterprise Linux | Red Hat OpenShift | Red Hat WildFly | Redmine | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | نرم‌افزار مدیریت منابع | Ruby | Ruby on Rails | SAP Business Objects | SAP Crystal Reports | SAP ERP | نرم‌افزار SAP | SAS | Salesforce Visualforce | Salesforce software | Scala | نرم‌افزار زمان‌بندی | Sciforma | Screencast-O-Matic | Selenium | ServiceNow | SharedPlan Software SharedPlan Pro | Shell script | Siemens Teamcenter | Skype | Slack | SmartBear Software Automated Build Studio | Smartsheet | Splunk Enterprise | Spring Boot | Spring Framework | Standpipe Studios Vertabase | StataCorp Stata | زبان پرس‌وجوی ساختاریافته SQL | Stylite eGroupWare | نرم‌افزار کنترل نظارتی و جمع‌آوری داده SCADA | Swift | Tableau | TaskJuggler | نرم‌افزار مالیاتی | TeamDynamixHE | Tenrox Project Workforce Management | Teradata Database | The MathWorks MATLAB | The Omni Group OmniPlan | ThoughtWorks Studio Mingle | Tigris Cabie | Transact-SQL | Trimble SketchUp Pro | UNIX | UNIX Shell | Ubuntu | Unawave | زبان مدل‌سازی یکپارچه UML | VMware | VSCOnline VPMi | Veritas NetBackup | نرم‌افزار کنترل نسخه | نرم‌افزار شبکه خصوصی مجازی VPN | Vitria M3O Operational Intelligence | نرم‌افزار سیستم انتقال صدا روی پروتکل اینترنت VoIP | WBS Goplan | Wireshark | Wrike | Xplanner | Zoho Projects | dotProject | easyCIS | i-lign | jQuery | pm ase QuickBuild | web2project</t>
+          <t>24SevenOffice Project | 3M Post-it App | AEC Software FastTrack Schedule | AJAX | AMS REALTIME Projects | Actano Rplan | Adobe Acrobat | Adobe ActionScript | نرم‌افزار Adobe Creative Cloud | Adobe Dreamweaver | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | برنامه‌نویسی پیشرفته برنامه‌های تجاری ABAP | Airtable | Amazon DynamoDB | Amazon Elastic Compute Cloud EC2 | Amazon Kinesis | Amazon Redshift | نرم‌افزار Amazon Web Services AWS | نرم‌افزار Ansible | AnthillPro | Apache Ant | Apache Cassandra | Apache Continuum | Apache Groovy | Apache Gump | Apache HTTP Server | Apache Hadoop | Apache Hive | Apache Kafka | Apache Maven | Apache Pig | Apache Solr | Apache Spark | Apache Struts | Apache Subversion SVN | Apache Tomcat | Apple Final Cut Pro | Apple macOS | Ascensio Systems TeamLab | Assembla | AtTask | Atlassian Bamboo | Atlassian Confluence | Atlassian JIRA | Autodesk AutoCAD | Autodesk Revit | Automation Centre TrackerSuite.Net | Backbone.js | Basecamp | Bash | Blackbaud The Raiser's Edge | نرم‌افزار Blackboard | BrightWork pmPoint | C | C# | C++ | CA Technologies CA Clarity PPM for IT Governance | CS Odessa ConceptDraw Project | Canonical Launchpad | برگه‌های سبک آبشاری CSS | Central Desktop | Chef | Cisco IOS | Cisco Webex | نرم‌افزار رایانش ابری Citrix | Clarity Systems IBM Clarity | Clarizen | نرم‌افزار میزبانی کد | نرم‌افزار مدیریت چرخه حیات برنامه مشارکتی ALM | زبان مشترک تجاری COBOL | نرم‌افزار یکپارچه‌سازی مداوم | Countersoft Gemini | CruiseControl | سیستم کنترل اطلاعات مشتری CICS | Daptiv PPM | Dassault Systemes CATIA | Delphi Technology | Digital Crew Teamwork Project Manager | Disarea 5pm | Django | Docker | نرم‌افزار سیستم مدیریت اسناد | Drupal | زبان نشانه‌گذاری ابرمتن پویا DHTML | نرم‌افزار ESRI ArcGIS | Eclipse IDE | Edgewell Trac | Edulastic | Elasticsearch | ElectricCloud ElectricCommander | Element Software Copper | Endeavour Agile ALM | Enterprise JavaBeans | Epic Systems | Experience in Software Project KickStart | Ext JS | زبان نشانه‌گذاری ابرمتن توسعه‌پذیر XHTML | زبان نشانه‌گذاری توسعه‌پذیر XML | Facebook | Feng Office Collaboration Platform | FileMaker Pro | FinalBuilder | Fog Creek Software FogBugz | Forum One Communications ProjectSpaces | GanttProject | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Git | GitHub | Glasscubes | Go | Google Ads | Google Analytics | Google Angular | Google Docs | Google Drive | Google Meet | سیستم کدگذاری رویه‌های رایج مراقبت‌های بهداشتی HCPCS | Hewlett Packard HP Project Portfolio Management Solution | Hewlett Packard HP-UX | Hewlett Packard LoadRunner | Hibernate ORM | نرم‌افزار مدیریت منابع انسانی HRMS | HyperOffice Collaboration Suite | زبان نشانه‌گذاری ابرمتن HTML | IBM Cognos Impromptu | IBM DB2 | IBM Domino | IBM InfoSphere DataStage | IBM Notes | نرم‌افزار IBM Power Systems | IBM Rational Build Forge | IBM SPSS Statistics | IBM Software Configuration and Library Manager SCLM | IBM WebSphere | IBM WebSphere MQ | InLoox | نرم‌افزار محیط توسعه یکپارچه IDE | Intellisys Project Desktop | Intland Software codeBeamer | نرم‌افزار سیستم ردیابی مشکلات | JUnit | JamBoard | JavaScript | JavaScript Object Notation JSON | JetBrains Team City | زبان کنترل کار JCL | Jupyter Notebook | KOffice.org Kplato | Kforge | Kidasa Milestones Professional | KommandCore | KornShell | LAMP Stack | LexisNexis | Linux | LiquidPlanner | LogMeIn GoToMeeting | Logic Software Easy Projects.NET | LuntBuild | MPI Micro Planner X-Pert | Madrigal Soft Tools Delegator | MantisBT | Marketo Marketing Automation | MatchWare MindView | McAfee | MicroStrategy | Microsoft .NET Framework | Microsoft ASP.NET | Microsoft ASP.NET Core MVC | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft ActiveX | نرم‌افزار Microsoft Azure | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft OneNote | Microsoft Outlook | Microsoft PowerPoint | Microsoft PowerShell | Microsoft Project | Microsoft Publisher | Microsoft SQL Server | Microsoft SQL Server Integration Services SSIS | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Team Foundation Server | Microsoft Teams | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Basic for Applications VBA | Microsoft Visual Studio | Microsoft Windows | Microsoft Windows Server | Microsoft Word | نرم‌افزار نقشه‌برداری ذهنی | MindGenius | Minitab | MinuteMan Systems MinuteMan Project Management Software | MongoDB | MySQL | Nagios | NetSuite ERP | Ninian Huddle | NoSQL | Node.js | نرم‌افزار امنیت سایبری NortonLifeLock | NovaMind Merlin Project Manager | O3spaces Workplace | Objective C | Objective Decision Contactizer Pro | OfficeWork Software TurboProject | Open Dynamics Collabtive | OpenMake Software Meister | OpenMake Software Mojo | Oracle Business Intelligence Enterprise Edition | Oracle Database | Oracle E-Business Suite Financials | Oracle Eloqua | Oracle Fusion Applications | Oracle Fusion Middleware | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle JDBC | Oracle Java | Oracle Java 2 Platform Enterprise Edition J2EE | Oracle JavaServer Pages JSP | Oracle PL/SQL | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Primavera Enterprise Project Portfolio Management | Oracle Primavera P6 Professional Project Management | Oracle Solaris | Oracle Taleo | Oracle WebLogic Server | PHP | Palbridge Ubidesk | نرم‌افزار Perforce Helix | Perl | Planbox | Planisware | Planview Process Builder | PostgreSQL | Project Manager Online ProjectManager.com | نرم‌افزار مدیریت سبد پروژه PPM | Project-Open | Project.net | ProjectLibre | Projecturf | Puppet | Python | QSM SLIM Suite | Qlik Tech QlikView | Quest Erwin Data Modeler | نرم‌افزار مدیریت کسب‌وکار QuickBase | R | React | Red Hat Enterprise Linux | Red Hat OpenShift | Red Hat WildFly | Redmine | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | نرم‌افزار مدیریت منابع | Ruby | Ruby on Rails | SAP Business Objects | SAP Crystal Reports | SAP ERP | نرم‌افزار SAP | SAS | Salesforce Visualforce | نرم‌افزار Salesforce | Scala | نرم‌افزار زمان‌بندی | Sciforma | Screencast-O-Matic | Selenium | ServiceNow | SharedPlan Software SharedPlan Pro | Shell script | Siemens Teamcenter | Skype | Slack | SmartBear Software Automated Build Studio | Smartsheet | Splunk Enterprise | Spring Boot | Spring Framework | Standpipe Studios Vertabase | StataCorp Stata | زبان پرس‌وجوی ساختاریافته SQL | Stylite eGroupWare | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | Swift | Tableau | TaskJuggler | نرم‌افزار مالیاتی | TeamDynamixHE | Tenrox Project Workforce Management | Teradata Database | The MathWorks MATLAB | The Omni Group OmniPlan | ThoughtWorks Studio Mingle | Tigris Cabie | Transact-SQL | Trimble SketchUp Pro | UNIX | UNIX Shell | Ubuntu | Unawave | زبان مدل‌سازی یکپارچه UML | VMware | VSCOnline VPMi | Veritas NetBackup | نرم‌افزار کنترل نسخه | نرم‌افزار شبکه خصوصی مجازی VPN | Vitria M3O Operational Intelligence | نرم‌افزار سیستم انتقال صدا روی پروتکل اینترنت VoIP | WBS Goplan | Wireshark | Wrike | Xplanner | Zoho Projects | dotProject | easyCIS | i-lign | jQuery | pm ase QuickBuild | web2project</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نگارش | گوش دادن فعال | درک مطلب | سخن گفتن | پایش | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | نگارش | گوش دادن فعال | درک مطلب | سخن گفتن | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | خدمات مشتریان و پرسنل | رایانه و الکترونیک | مدیریت و سازماندهی | مهندسی و فناوری | اقتصاد و حسابداری | امور اداری | مخابرات | ریاضیات | پرسنل و منابع انسانی | ارتباطات و رسانه</t>
+          <t>زبان انگلیسی | خدمات مشتری و شخصی | رایانه و الکترونیک | مدیریت و اداره | مهندسی و فناوری | اقتصاد و حسابداری | اداری | مخابرات | ریاضیات | پرسنل و منابع انسانی | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال استنتاجی | استدلال استقرایی | سازماندهی اطلاعات | درک شفاهی | روانی ایده‌ها | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | اصالت | انعطاف‌پذیری دسته‌بندی | سهولت در کار با اعداد | انعطاف‌پذیری بستار | استدلال ریاضی</t>
+          <t>درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | درک شفاهی | روانی ایده‌ها | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | اصالت | انعطاف‌پذیری دسته‌بندی | توانایی عددی | انعطاف‌پذیری بستار | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | صرف زمان به صورت نشسته | محیط داخلی، کنترل‌شده از نظر دما | تعیین وظایف، اولویت‌ها و اهداف | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فشار زمانی | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | آزادی در تصمیم‌گیری | پیامدهای کاری و نتایج سایر کارکنان | اهمیت دقیق یا منظم بودن | سطح رقابت | تاثیر تصمیمات بر همکاران یا نتایج شرکت | موقعیت‌های تعارض | نامه‌ها و یادداشت‌های کتبی | تناوب تصمیم‌گیری | سروکار داشتن با مشتریان خارجی یا عموم مردم به صورت عمومی | اهمیت تکرار وظایف یکسان</t>
+          <t>ایمیل | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | صرف زمان برای نشستن | محیط داخلی، دارای کنترل شرایط محیطی | تعیین وظایف، اولویت‌ها و اهداف | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فشار زمانی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | آزادی در تصمیم‌گیری | پیامدهای کاری و نتایج سایر کارکنان | اهمیت دقیق یا درست بودن | سطح رقابت | تأثیر تصمیمات بر همکاران یا نتایج شرکت | موقعیت‌های تعارض | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | اهمیت تکرار وظایف یکسان</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | مدیران معماری و مهندسی | برنامه‌ریزان تداوم کسب‌وکار | تحلیلگران سیستم‌های رایانه‌ای | مهندسان/معماران سیستم‌های رایانه‌ای | مدیران سیستم‌های رایانه‌ای و اطلاعاتی | مدیران پایگاه داده | معماران پایگاه داده | متخصصان مدیریت اسناد | سرپرستان خط اول کارکنان پشتیبانی اداری و دفتری | مدیران کل و عملیاتی | مهندسان صنایع | مهندسان لجستیک | تحلیلگران مدیریت | مدیران شبکه و سیستم‌های رایانه‌ای | تحلیلگران تحقیق در عملیات | متخصصان مدیریت پروژه | توسعه‌دهندگان نرم‌افزار | مدیران نصب انرژی خورشیدی | مدیران وب</t>
+          <t>مدیران خدمات اداری | مدیران معماری و مهندسی | برنامه‌ریزان تداوم کسب‌وکار | تحلیلگران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | مدیران کامپیوتر و سیستم‌های اطلاعاتی | مدیران پایگاه داده | معماران پایگاه داده | متخصصان مدیریت اسناد | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | مدیران عمومی و عملیات | مهندسان صنایع | مهندسان لجستیک | تحلیل‌گران مدیریت | مدیران شبکه و سیستم‌های کامپیوتری | تحلیل‌گران تحقیق در عملیات | متخصصان مدیریت پروژه | توسعه‌دهندگان نرم‌افزار | مدیران نصب انرژی خورشیدی | مدیران وب</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Actuaries</t>
+          <t>کارشناسان آمار بیمه (اکچوئری) (Actuaries)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | ریاضیات | درک مطلب | گوش دادن فعال | سخن گفتن | نگارش | یادگیری فعال | پایش</t>
+          <t>تفکر انتقادی | ریاضیات | درک مطلب | گوش دادن فعال | سخن گفتن | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -917,17 +917,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>استدلال ریاضی | استدلال استقرایی | سهولت در کار با اعداد | درک شفاهی | درک کتبی | بیان کتبی | استدلال استنتاجی | انعطاف‌پذیری دسته‌بندی | بیان شفاهی | حساسیت به مسئله | سازماندهی اطلاعات | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری بستار | توجه انتخابی | روانی ایده‌ها</t>
+          <t>استدلال ریاضی | استدلال استقرایی | توانایی عددی | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | بیان شفاهی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری بستار | توجه انتخابی | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ایمیل | محیط داخلی، کنترل‌شده از نظر دما | صرف زمان به صورت نشسته | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | اهمیت دقیق یا منظم بودن | کار با یا مشارکت در یک گروه کاری یا تیم | تاثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | ارتباط با دیگران | سطح رقابت</t>
+          <t>ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | ارتباط با دیگران | سطح رقابت</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | تحلیلگران هوش تجاری | مدیران جبران خدمات و مزایا | متخصصان جبران خدمات، مزایا و تحلیل شغل | تحلیلگران اعتبار | اقتصاددانان | بازرسان مالی | مدیران مالی | تحلیلگران کمی مالی | متخصصان ریسک مالی | تحلیلگران مالی و سرمایه‌گذاری | نمایندگان فروش بیمه | پذیره‌نویسان بیمه | مدیران صندوق‌های سرمایه‌گذاری | تحلیلگران مدیریت | مشاوران مالی شخصی | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی | دستیاران آماری | آمارشناسان</t>
+          <t>حسابداران و حسابرسان | تحلیلگران هوش تجاری | مدیران جبران خدمات و مزایا | متخصصان جبران خدمات، مزایا و تحلیل شغل | تحلیلگران اعتبار | اقتصاددانان | بازرسان مالی | مدیران مالی | تحلیلگران کمی مالی | متخصصان ریسک مالی | تحلیلگران مالی و سرمایه‌گذاری | نمایندگان فروش بیمه | بیمه‌گران | مدیران صندوق سرمایه‌گذاری | تحلیل‌گران مدیریت | مشاوران مالی شخصی | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی | دستیاران آماری | آمارشناسان</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mathematicians</t>
+          <t>ریاضی‌دانان (Mathematicians)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -959,12 +959,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>AMPL | ARfit | Adobe Photoshop | Algae | Analyse-it | Analysis and Visualization of Time Sequences AVTS | Apfloat | Apple Shazam | Apple macOS | Aptech Systems GAUSS | Atlassian JIRA | Aztec | Bash | C | C# | C++ | برگه‌های سبک آبشاری CSS | نرم‌افزار چت‌بات | Computer Algebra System for Algebraic Geometry CASA | DSP Development DADiSP | نرم‌افزار بصری‌سازی داده‌ها | DataDescription DataDesk | DifEqu | Discrete Dynamics Lab DDLab | EleSoft Research | زبان نشانه‌گذاری گسترش‌پذیر XML | ترجمه فرمول/مترجم FORTRAN | GNU Octave | Geomview | GraphPad Software GraphPad Prism | Graphics Programming Environment GRAPE | زبان نشانه‌گذاری ابرمتن HTML | IBM SPSS Amos | IBM SPSS Statistics | Insightful S-PLUS | Interactive Mathematical Proof System IMPS | JACAL | JavaScript | KANT | KSEG | LINDO Systems LINDO API | Linux | MacKichan Software Scientific WorkPlace | نرم‌افزار Magma Design Automation | Maplesoft Maple | Mathsoft Mathcad | Maxima Software | Maximal Software MPL Modeling System | MicroPress VTeX | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Visual Basic | Microsoft Visual Studio | Microsoft Windows | Microsoft Word | Minitab | ModelKinetix ModelMaker | Multipath Corporation Fast Matrix Solver FMS | MySQL | Numeritek NUMERICA | نرم‌افزار محیط توسعه شیءگرا | Oracle Java | PARI/GP | PHP | نرم‌افزار Perforce | Perl | Polymath Software POLYMATH | Provalis Research Simstat | Python | R | SAS | STATISTICA | نرم‌افزار حسابداری Sage | Salesforce software | StataCorp Stata | زبان پرس‌وجوی ساختاریافته SQL | SuperANOVA | Symmetrica | Systat Software SigmaPlot | Tableau | The MathWizards MathViews | The MathWorks MATLAB | UNISTAT Statistical Package | UNIX | نرم‌افزار طراحی رابط کاربری | نرم‌افزار کنترل نسخه | Vormetric Application Encryption | نرم‌افزار مرورگر وب | نرم‌افزار وب سرور | Wolfram Research Mathematica</t>
+          <t>AMPL | ARfit | Adobe Photoshop | Algae | Analyse-it | Analysis and Visualization of Time Sequences AVTS | Apfloat | Apple Shazam | Apple macOS | Aptech Systems GAUSS | Atlassian JIRA | Aztec | Bash | C | C# | C++ | برگه‌های سبک آبشاری CSS | نرم‌افزار چت‌بات | Computer Algebra System for Algebraic Geometry CASA | DSP Development DADiSP | نرم‌افزار تجسم داده | DataDescription DataDesk | DifEqu | Discrete Dynamics Lab DDLab | EleSoft Research | زبان نشانه‌گذاری توسعه‌پذیر XML | Formula translation/translator FORTRAN | GNU Octave | Geomview | GraphPad Software GraphPad Prism | Graphics Programming Environment GRAPE | زبان نشانه‌گذاری ابرمتن HTML | IBM SPSS Amos | IBM SPSS Statistics | Insightful S-PLUS | Interactive Mathematical Proof System IMPS | JACAL | JavaScript | KANT | KSEG | LINDO Systems LINDO API | Linux | MacKichan Software Scientific WorkPlace | نرم‌افزار Magma Design Automation | Maplesoft Maple | Mathsoft Mathcad | Maxima Software | Maximal Software MPL Modeling System | MicroPress VTeX | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Visual Basic | Microsoft Visual Studio | Microsoft Windows | Microsoft Word | Minitab | ModelKinetix ModelMaker | Multipath Corporation Fast Matrix Solver FMS | MySQL | Numeritek NUMERICA | نرم‌افزار محیط توسعه شیءگرا | Oracle Java | PARI/GP | PHP | نرم‌افزار Perforce | Perl | Polymath Software POLYMATH | Provalis Research Simstat | Python | R | SAS | STATISTICA | نرم‌افزار حسابداری Sage | نرم‌افزار Salesforce | StataCorp Stata | زبان پرس‌وجوی ساختاریافته SQL | SuperANOVA | Symmetrica | Systat Software SigmaPlot | Tableau | The MathWizards MathViews | The MathWorks MATLAB | UNISTAT Statistical Package | UNIX | نرم‌افزار طراحی رابط کاربری | نرم‌افزار کنترل نسخه | Vormetric Application Encryption | نرم‌افزار مرورگر وب | نرم‌افزار وب سرور | Wolfram Research Mathematica</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ریاضیات | تفکر انتقادی | درک مطلب | یادگیری فعال | علوم | نگارش | گوش دادن فعال | راهبردهای یادگیری | سخن گفتن | پایش</t>
+          <t>ریاضیات | تفکر انتقادی | درک مطلب | یادگیری فعال | علوم | نگارش | گوش دادن فعال | راهبردهای یادگیری | سخن گفتن | نظارت</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -974,17 +974,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>استدلال ریاضی | سهولت در کار با اعداد | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال استنتاجی | استدلال استقرایی | سازماندهی اطلاعات | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | حساسیت به مسئله | بینایی نزدیک | انعطاف‌پذیری بستار | توجه انتخابی | وضوح گفتار | تشخیص گفتار</t>
+          <t>استدلال ریاضی | توانایی عددی | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | حساسیت به مسئله | بینایی نزدیک | انعطاف‌پذیری بستار | توجه انتخابی | وضوح گفتار | تشخیص گفتار</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ایمیل | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا منظم بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان به صورت نشسته | سطح رقابت | محیط داخلی، کنترل‌شده از نظر دما</t>
+          <t>ایمیل | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای نشستن | سطح رقابت | محیط داخلی، دارای کنترل شرایط محیطی</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>اخترشناسان | زیست‌شیمی‌دانان و زیست‌فیزیک‌دانان | مهندسان زیست‌پزشکی و بیومدیکال | دانشمندان بیوانفورماتیک | تکنسین‌های بیوانفورماتیک | زیست‌آمارشناسان | دانشمندان پژوهشگر رایانه و اطلاعات | دانشمندان داده | تحلیلگران کمی مالی | ژنتیک‌دانان | زمین‌شناسان، به جز آب‌شناسان و جغرافیدانان | معلمان علوم ریاضی، پس از متوسطه | زیست‌شناسان سلولی و مولکولی | مهندسان نانوسیستم‌ها | تحلیلگران تحقیق در عملیات | فیزیک‌دانان | معلمان فیزیک، پس از متوسطه | توسعه‌دهندگان نرم‌افزار | دستیاران آماری | آمارشناسان</t>
+          <t>اخترشناسان | بیوشیمی‌دانان و بیوفیزیک‌دانان | مهندسان زیستی و مهندسان زیست‌پزشکی | دانشمندان بیوانفورماتیک | تکنسین‌های بیوانفورماتیک | آمارشناسان زیستی | دانشمندان تحقیقات کامپیوتر و اطلاعات | دانشمندان داده | تحلیلگران کمی مالی | ژنتیک‌دان‌ها | زمین‌شناسان، به‌جز آب‌شناسان و جغرافی‌دانان | مدرسان علوم ریاضی، پس از متوسطه | زیست‌شناسان مولکولی و سلولی | مهندسان نانوسیستم | تحلیل‌گران تحقیق در عملیات | فیزیکدانان | مدرسان فیزیک، پس از متوسطه | توسعه‌دهندگان نرم‌افزار | دستیاران آماری | آمارشناسان</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Operations Research Analysts</t>
+          <t>تحلیل‌گران تحقیق در عملیات (Operations Research Analysts)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>A mathematical programming language AMPL | Amazon Redshift | Apache Hadoop | Apache Hive | Apache Pig | Apple macOS | Bash | Blackbaud The Raiser's Edge | Business Forecast Systems Forecast Pro | C | C++ | Cisco IOS | نرم‌افزار رایانش ابری Citrix | Claritas PRIZM NE | Dassault Systemes CATIA | نرم‌افزار ورود داده | نرم‌افزار پایگاه داده | ESRI ArcExplorer | نرم‌افزار ESRI ArcGIS | Eko | زبان نشانه‌گذاری گسترش‌پذیر XML | FileMaker Pro | نرم‌افزار حسابداری صندوق | General algebraic modeling system GAMS | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | GitHub | Google Docs | Google Drive | Google Slides | Hewlett Packard HP-UX | نرم‌افزار مدیریت منابع انسانی HRMS | Hyperion Solutions Hyperion Intelligence | IBM Cognos Impromptu | IBM Domino | IBM Notes | نرم‌افزار IBM Power Systems | IBM SPSS Statistics | ILOG OPL-CPLEX Development System | Imagine That Extend OR | Insightful S-PLUS | زبان کنترل کار JCL | Jupyter Notebook | LINDO Systems LINGO | LexisNexis | Linux | Marketo Marketing Automation | MathWorks Simulink | Mathsoft Mathcad | McAfee | Mesquite Software CSIM | MicroStrategy | Microsoft Access | Microsoft Dynamics | Microsoft Excel | Microsoft Exchange | Microsoft MapPoint | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Power BI | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Basic for Applications VBA | Microsoft Word | Minitab | Mixed integer optimizer MINTO | MySQL | National Instruments LabVIEW | NetSuite ERP | Oracle Business Intelligence Enterprise Edition | Oracle E-Business Suite Financials | Oracle Eloqua | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | Oracle Solaris | Oracle Taleo | Perl | ProModel | Python | Qlik Tech QlikView | R | Rockwell Automation Arena | SAP Business Objects | SAP Crystal Reports | SAP PowerBuilder | نرم‌افزار SAP | SAS | Salesforce software | Scala | Shell script | Splunk Enterprise | Stanford Business Software MINOS | Stanford Business Software SNOPT | StataCorp Stata | Strategic Reporting Systems ReportSmith | زبان پرس‌وجوی ساختاریافته SQL | Sun Microsystems Java | Swift | Tableau | Telelogic System Architect | Teradata Database | The MathWorks MATLAB | UNIX | UNIX Shell | Veritas NetBackup | Wireshark | Wolfram Research Mathematica | iGrafx</t>
+          <t>A mathematical programming language AMPL | Amazon Redshift | Apache Hadoop | Apache Hive | Apache Pig | Apple macOS | Bash | Blackbaud The Raiser's Edge | Business Forecast Systems Forecast Pro | C | C++ | Cisco IOS | نرم‌افزار رایانش ابری Citrix | Claritas PRIZM NE | Dassault Systemes CATIA | نرم‌افزار ورود داده | نرم‌افزار پایگاه داده | ESRI ArcExplorer | نرم‌افزار ESRI ArcGIS | Eko | زبان نشانه‌گذاری توسعه‌پذیر XML | FileMaker Pro | نرم‌افزار حسابداری صندوق | General algebraic modeling system GAMS | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | GitHub | Google Docs | Google Drive | Google Slides | Hewlett Packard HP-UX | نرم‌افزار مدیریت منابع انسانی HRMS | Hyperion Solutions Hyperion Intelligence | IBM Cognos Impromptu | IBM Domino | IBM Notes | نرم‌افزار IBM Power Systems | IBM SPSS Statistics | ILOG OPL-CPLEX Development System | Imagine That Extend OR | Insightful S-PLUS | زبان کنترل کار JCL | Jupyter Notebook | LINDO Systems LINGO | LexisNexis | Linux | Marketo Marketing Automation | MathWorks Simulink | Mathsoft Mathcad | McAfee | Mesquite Software CSIM | MicroStrategy | Microsoft Access | Microsoft Dynamics | Microsoft Excel | Microsoft Exchange | Microsoft MapPoint | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Power BI | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Basic for Applications VBA | Microsoft Word | Minitab | Mixed integer optimizer MINTO | MySQL | National Instruments LabVIEW | NetSuite ERP | Oracle Business Intelligence Enterprise Edition | Oracle E-Business Suite Financials | Oracle Eloqua | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | Oracle Solaris | Oracle Taleo | Perl | ProModel | Python | Qlik Tech QlikView | R | Rockwell Automation Arena | SAP Business Objects | SAP Crystal Reports | SAP PowerBuilder | نرم‌افزار SAP | SAS | نرم‌افزار Salesforce | Scala | Shell script | Splunk Enterprise | Stanford Business Software MINOS | Stanford Business Software SNOPT | StataCorp Stata | Strategic Reporting Systems ReportSmith | زبان پرس‌وجوی ساختاریافته SQL | Sun Microsystems Java | Swift | Tableau | Telelogic System Architect | Teradata Database | The MathWorks MATLAB | UNIX | UNIX Shell | Veritas NetBackup | Wireshark | Wolfram Research Mathematica | iGrafx</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1026,22 +1026,22 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ریاضیات | رایانه و الکترونیک | مهندسی و فناوری | تولید و پردازش | زبان انگلیسی | طراحی | آموزش و پرورش</t>
+          <t>ریاضیات | رایانه و الکترونیک | مهندسی و فناوری | تولید و فرآوری | زبان انگلیسی | طراحی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>استدلال ریاضی | استدلال استنتاجی | استدلال استقرایی | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | سهولت در کار با اعداد | سازماندهی اطلاعات | بینایی نزدیک | روانی ایده‌ها | اصالت | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری بستار | توجه انتخابی</t>
+          <t>استدلال ریاضی | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | توانایی عددی | ترتیب‌دهی اطلاعات | بینایی نزدیک | روانی ایده‌ها | اصالت | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری بستار | توجه انتخابی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>محیط داخلی، کنترل‌شده از نظر دما | ایمیل | صرف زمان به صورت نشسته | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا منظم بودن | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | سطح رقابت | ارتباط با دیگران | فشار زمانی | تاثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | ایمیل | صرف زمان برای نشستن | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | سطح رقابت | ارتباط با دیگران | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>تحلیلگران هوش تجاری | تحلیلگران سیستم‌های رایانه‌ای | مهندسان/معماران سیستم‌های رایانه‌ای | دانشمندان پژوهشگر رایانه و اطلاعات | دانشمندان داده | متخصصان انبارش داده | مدیران پایگاه داده | معماران پایگاه داده | تحلیلگران کمی مالی | متخصصان ریسک مالی | فن‌آوران اطلاعات سلامت و ثبت‌کنندگان پزشکی | مهندسان صنایع | مهندسان لجستیک | تحلیلگران مدیریت | ریاضی‌دانان | متخصصان مدیریت پروژه | توسعه‌دهندگان نرم‌افزار | تحلیلگران و تست‌کنندگان تضمین کیفیت نرم‌افزار | دستیاران آماری | آمارشناسان</t>
+          <t>تحلیلگران هوش تجاری | تحلیلگران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | دانشمندان تحقیقات کامپیوتر و اطلاعات | دانشمندان داده | متخصصان انبارش داده | مدیران پایگاه داده | معماران پایگاه داده | تحلیلگران کمی مالی | متخصصان ریسک مالی | فن‌آوران اطلاعات سلامت و ثبت‌کنندگان پزشکی | مهندسان صنایع | مهندسان لجستیک | تحلیل‌گران مدیریت | ریاضی‌دانان | متخصصان مدیریت پروژه | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و تست‌کنندگان تضمین کیفیت نرم‌افزار | دستیاران آماری | آمارشناسان</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0014_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0014_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | نگارش | تفکر انتقادی | نظارت | یادگیری فعال | سخن گفتن | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | گوش دادن فعال | نگارش | تفکر انتقادی | نظارت | یادگیری فعال | سخن گفتن | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | مدیریت و امور اداری | رایانه و الکترونیک | خدمات مشتریان و خدمات فردی | امور اداری | امور حقوقی و دولتی | آموزش و تدریس</t>
+          <t>زبان انگلیسی | مدیریت و اداره | رایانه و الکترونیک | خدمات مشتری و شخصی | اداری | قانون و دولت | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | مرتب‌سازی اطلاعات | استدلال قیاسی | دید نزدیک | انعطاف‌پذیری در طبقه‌بندی | تشخیص گفتار | وضوح گفتار | روان بودن ایده‌ها | وضوح گفتار | توجه انتخابی | ابتکار و اصالت</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | ترتیب‌دهی اطلاعات | استدلال قیاسی | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | تشخیص گفتار | انعطاف‌پذیری بستار | روانی ایده‌ها | وضوح گفتار | توجه انتخابی | اصالت</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | تحلیل‌گران هوش تجاری | مدیران داده‌های بالینی | مدیران انطباق و نظارت | تحلیل‌گران سامانه‌های رایانه‌ای | مدیران فناوری اطلاعات و سامانه‌های رایانه‌ای | متصدیان ورود اطلاعات | کارشناسان پایگاه داده و انبار داده | مدیران پایگاه داده | مهندسان معمار پایگاه داده | متصدیان بایگانی و سوابق | متخصصان فناوری اطلاعات سلامت و ثبت اطلاعات پزشکی | تحلیل‌گران امنیت اطلاعات | تحلیل‌گران مدیریت | متخصصان اسناد و مدارک پزشکی | متصدیان امور اداری و دفتری | توسعه‌دهندگان نرم‌افزار | دستیاران آمار | نویسندگان متون فنی | مدیران پایگاه‌های اینترنتی</t>
+          <t>مدیران خدمات اداری و پشتیبانی | تحلیل‌گران هوش تجاری | مدیران داده‌های بالینی | مدیران تطبیق و نظارت مقرراتی | تحلیل‌گران سیستم‌های کامپیوتری | مدیران فناوری اطلاعات و سیستم‌های رایانه‌ای | متصدیان ورود اطلاعات و داده‌آمایی | متخصصان انباره داده | مدیران پایگاه داده | معماران پایگاه داده | متصدیان بایگانی و اسناد | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | تحلیل‌گران امنیت اطلاعات | کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان و تکنسین‌های مدارک پزشکی و فناوری اطلاعات سلامت | متصدیان امور دفتری و امور عمومی اداری | توسعه‌دهندگان نرم‌افزار | دستیاران و تکنسین‌های آمار | نویسندگان متون فنی | مدیران وب</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | شنیدن فعال | سخن گفتن | ریاضیات | یادگیری فعال | نگارش | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | مخابرات و ارتباطات | زبان انگلیسی | ریاضیات | مهندسی و فناوری | امور حقوقی و دولتی | ایمنی و امنیت عمومی | مدیریت و امور اداری</t>
+          <t>رایانه و الکترونیک | مخابرات | زبان انگلیسی | ریاضیات | مهندسی و فناوری | قانون و دولت | ایمنی و امنیت عمومی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری در طبقه‌بندی | روان بودن ایده‌ها | ابتکار و اصالت | توجه انتخابی | تسهیم زمان | تجسم‌سازی | حافظه و یادسپاری | استدلال ریاضی | تسلط بر کار با اعداد | سرعت ادراک | وضوح گفتار</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن | استدلال ریاضی | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مهندسان زنجیره بلوکی (بلاک‌چین) | مهندسان معمار شبکه | کارشناسان پشتیبانی شبکه | تحلیل‌گران سامانه‌های رایانه‌ای | مهندسان و معماران سامانه‌های رایانه‌ای | مدیران فناوری اطلاعات و سامانه‌های رایانه‌ای | مدیران پایگاه داده | مهندسان معمار پایگاه داده | تحلیل‌گران جرم‌یابی دیجیتال | مهندسان بهداشت و ایمنی حرفه‌ای | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | تحلیل‌گران تهدیدات و اطلاعات سایبری | راهبران شبکه و سامانه‌های رایانه‌ای | کارشناسان تحلیل و کنترل کیفیت | کارشناسان مدیریت امنیت | مدیران امنیت اطلاعات | توسعه‌دهندگان نرم‌افزار | کارشناسان تضمین کیفیت و آزمون نرم‌افزار | مهندسان اعتبارسنجی سامانه‌ها</t>
+          <t>مهندسان زنجیره بلوکی | معماران شبکه رایانه‌ای | متخصصان پشتیبانی شبکه رایانه‌ای | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | مدیران فناوری اطلاعات و سیستم‌های رایانه‌ای | مدیران پایگاه داده | معماران پایگاه داده | تحلیل‌گران جرم‌یابی دیجیتال و پاسخ به حوادث | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معدن | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | تحلیل‌گران داده‌ها و اطلاعات امنیتی | مدیران شبکه و سیستم‌های کامپیوتری | کارشناسان تحلیل کنترل کیفیت | کارشناسان مدیریت حراست و امنیت فیزیکی | مدیران حراست و انتظامات | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و آزمون‌گران تضمین کیفیت نرم‌افزار | مهندسان اعتبارسنجی و صحه‌گذاری</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | نگارش | نظارت | سخن گفتن | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | نگارش | نظارت | سخن گفتن | یادگیری فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | مهندسی و فناوری | زبان انگلیسی | مخابرات و ارتباطات | خدمات مشتریان و خدمات فردی</t>
+          <t>رایانه و الکترونیک | مهندسی و فناوری | زبان انگلیسی | مخابرات | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | مرتب‌سازی اطلاعات | تشخیص گفتار | حساسیت به مسئله | دید نزدیک | استدلال استقرایی | بیان کتبی | وضوح گفتار | وضوح گفتار | توجه انتخابی | سرعت ادراک | انعطاف‌پذیری در طبقه‌بندی | روان بودن ایده‌ها</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | ترتیب‌دهی اطلاعات | تشخیص گفتار | حساسیت به مسئله | بینایی نزدیک | استدلال استقرایی | بیان کتبی | وضوح گفتار | انعطاف‌پذیری بستار | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مهندسان زنجیره بلوکی (بلاک‌چین) | مهندسان معمار شبکه | کارشناسان پشتیبانی شبکه | تحلیل‌گران سامانه‌های رایانه‌ای | مهندسان و معماران سامانه‌های رایانه‌ای | کارشناسان پشتیبانی کاربران رایانه | مدیران فناوری اطلاعات و سامانه‌های رایانه‌ای | مدیران پایگاه داده | مهندسان معمار پایگاه داده | تحلیل‌گران جرم‌یابی دیجیتال | تحلیل‌گران امنیت اطلاعات | تحلیل‌گران تهدیدات و اطلاعات سایبری | راهبران شبکه و سامانه‌های رایانه‌ای | متخصصان آزمون نفوذپذیری و ارزیابی امنیتی | کارشناسان مدیریت امنیت | مدیران امنیت اطلاعات | توسعه‌دهندگان نرم‌افزار | کارشناسان تضمین کیفیت و آزمون نرم‌افزار | متخصصان مهندسی مخابرات | مدیران پایگاه‌های اینترنتی</t>
+          <t>مهندسان زنجیره بلوکی | معماران شبکه رایانه‌ای | متخصصان پشتیبانی شبکه رایانه‌ای | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | متخصصان پشتیبانی کاربران رایانه | مدیران فناوری اطلاعات و سیستم‌های رایانه‌ای | مدیران پایگاه داده | معماران پایگاه داده | تحلیل‌گران جرم‌یابی دیجیتال و پاسخ به حوادث | تحلیل‌گران امنیت اطلاعات | تحلیل‌گران داده‌ها و اطلاعات امنیتی | مدیران شبکه و سیستم‌های کامپیوتری | متخصصان آزمون نفوذپذیری و ارزیابی امنیتی | کارشناسان مدیریت حراست و امنیت فیزیکی | مدیران حراست و انتظامات | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و آزمون‌گران تضمین کیفیت نرم‌افزار | متخصصان مهندسی مخابرات | مدیران وب</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | شنیدن فعال | سخن گفتن | ریاضیات | یادگیری فعال | نگارش | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | امور حقوقی و دولتی | زبان انگلیسی | مخابرات و ارتباطات | ایمنی و امنیت عمومی | ریاضیات | مهندسی و فناوری | مدیریت و امور اداری</t>
+          <t>رایانه و الکترونیک | قانون و دولت | زبان انگلیسی | مخابرات | ایمنی و امنیت عمومی | ریاضیات | مهندسی و فناوری | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری در طبقه‌بندی | روان بودن ایده‌ها | ابتکار و اصالت | توجه انتخابی | تسهیم زمان | تجسم‌سازی | حافظه و یادسپاری | استدلال ریاضی | تسلط بر کار با اعداد | سرعت ادراک | وضوح گفتار</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن | استدلال ریاضی | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>تکنسین‌های بیوانفورماتیک | تحلیل‌گران هوش تجاری | مهندسان معمار شبکه | کارشناسان پشتیبانی شبکه | تحلیل‌گران سامانه‌های رایانه‌ای | مدیران فناوری اطلاعات و سامانه‌های رایانه‌ای | مدیران پایگاه داده | مهندسان معمار پایگاه داده | کارشناسان مدیریت اسناد و مدارک | کارشناسان آزمایشگاه تشخیص هویت و علوم جنایی | کارشناسان بازرسی، کشف و تحلیل تقلب | کارشناسان نظارت و بازرسی سامانه‌های کنترلی | کارشناسان و تکنسین‌های سیستم‌های اطلاعات جغرافیایی GIS | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | تحلیل‌گران تهدیدات و اطلاعات سایبری | متخصصان آزمون نفوذپذیری و ارزیابی امنیتی | افسران تشخیص هویت و امور پرونده‌ها در پلیس | کارشناسان مدیریت امنیت | مدیران امنیت اطلاعات</t>
+          <t>تکنسین‌های بیوانفورماتیک | تحلیل‌گران هوش تجاری | معماران شبکه رایانه‌ای | متخصصان پشتیبانی شبکه رایانه‌ای | تحلیل‌گران سیستم‌های کامپیوتری | مدیران فناوری اطلاعات و سیستم‌های رایانه‌ای | مدیران پایگاه داده | معماران پایگاه داده | کارشناسان مدیریت اسناد و مدارک | کاردان‌ها و تکنسین‌های علوم آزمایشگاهی و کشف علمی جرایم | کارشناسان بازرسی، کشف و تحلیل تقلب | ماموران و بازرسان نظارت تصویری و پایش اماکن سرگرمی و بازی | تکنسین‌ها و کارشناسان سیستم‌های اطلاعات جغرافیایی GIS | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | تحلیل‌گران داده‌ها و اطلاعات امنیتی | متخصصان آزمون نفوذپذیری و ارزیابی امنیتی | کارشناسان تشخیص هویت و ثبت سوابق پلیس | کارشناسان مدیریت حراست و امنیت فیزیکی | مدیران حراست و انتظامات</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | شنیدن فعال | سخن گفتن | ریاضیات | یادگیری فعال | نگارش | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | ریاضیات | زبان انگلیسی | مهندسی و فناوری | مخابرات و ارتباطات | اقتصاد و حسابداری | مدیریت و امور اداری | طراحی</t>
+          <t>رایانه و الکترونیک | ریاضیات | زبان انگلیسی | مهندسی و فناوری | مخابرات | اقتصاد و حسابداری | مدیریت و اداره | طراحی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری در طبقه‌بندی | روان بودن ایده‌ها | ابتکار و اصالت | توجه انتخابی | تسهیم زمان | تجسم‌سازی | حافظه و یادسپاری | استدلال ریاضی | تسلط بر کار با اعداد | سرعت ادراک | وضوح گفتار</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن | استدلال ریاضی | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>تحلیل‌گران هوش تجاری | مهندسان سخت‌افزار رایانه | مهندسان معمار شبکه | کارشناسان پشتیبانی شبکه | برنامه‌نویسان رایانه | تحلیل‌گران سامانه‌های رایانه‌ای | مهندسان و معماران سامانه‌های رایانه‌ای | کارشناسان پایگاه داده و انبار داده | مدیران پایگاه داده | مهندسان معمار پایگاه داده | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | مهندسان مکاترونیک | راهبران شبکه و سامانه‌های رایانه‌ای | متخصصان آزمون نفوذپذیری و ارزیابی امنیتی | توسعه‌دهندگان نرم‌افزار | کارشناسان تضمین کیفیت و آزمون نرم‌افزار | مدیران پایگاه‌های اینترنتی | توسعه‌دهندگان وب | طراحان رابط کاربری و وب</t>
+          <t>تحلیل‌گران هوش تجاری | مهندسان سخت‌افزار رایانه | معماران شبکه رایانه‌ای | متخصصان پشتیبانی شبکه رایانه‌ای | برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | متخصصان انباره داده | مدیران پایگاه داده | معماران پایگاه داده | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | مهندسان مکاترونیک | مدیران شبکه و سیستم‌های کامپیوتری | متخصصان آزمون نفوذپذیری و ارزیابی امنیتی | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و آزمون‌گران تضمین کیفیت نرم‌افزار | مدیران وب | توسعه‌دهندگان وب | طراحان وب و رابط‌های دیجیتال</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | درک مطلب | نگارش | سخن گفتن | یادگیری فعال | نظارت | استراتژی‌های یادگیری | علوم پایه | ریاضیات</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | نگارش | سخن گفتن | یادگیری فعال | نظارت | راهبردهای یادگیری | علوم | ریاضیات</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | زبان انگلیسی | مخابرات و ارتباطات | خدمات مشتریان و خدمات فردی | مهندسی و فناوری | مدیریت و امور اداری</t>
+          <t>رایانه و الکترونیک | زبان انگلیسی | مخابرات | خدمات مشتری و شخصی | مهندسی و فناوری | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | ابتکار و اصالت | دید نزدیک | روان بودن ایده‌ها | وضوح گفتار | انعطاف‌پذیری در طبقه‌بندی | وضوح گفتار | تسلط بر کار با اعداد | استدلال ریاضی | تشخیص گفتار | توجه انتخابی | سرعت ادراک</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | اصالت | بینایی نزدیک | روانی ایده‌ها | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | توانایی عددی | استدلال ریاضی | تشخیص گفتار | توجه انتخابی | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مهندسان زنجیره بلوکی (بلاک‌چین) | مهندسان سخت‌افزار رایانه | مهندسان معمار شبکه | کارشناسان پشتیبانی شبکه | برنامه‌نویسان رایانه | تحلیل‌گران سامانه‌های رایانه‌ای | کارشناسان پشتیبانی کاربران رایانه | مدیران فناوری اطلاعات و سامانه‌های رایانه‌ای | کارشناسان پایگاه داده و انبار داده | مدیران پایگاه داده | مهندسان معمار پایگاه داده | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | راهبران شبکه و سامانه‌های رایانه‌ای | متخصصان آزمون نفوذپذیری و ارزیابی امنیتی | کارشناسان مدیریت پروژه | توسعه‌دهندگان نرم‌افزار | کارشناسان تضمین کیفیت و آزمون نرم‌افزار | متخصصان مهندسی مخابرات | طراحان رابط کاربری و وب</t>
+          <t>مهندسان زنجیره بلوکی | مهندسان سخت‌افزار رایانه | معماران شبکه رایانه‌ای | متخصصان پشتیبانی شبکه رایانه‌ای | برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | متخصصان پشتیبانی کاربران رایانه | مدیران فناوری اطلاعات و سیستم‌های رایانه‌ای | متخصصان انباره داده | مدیران پایگاه داده | معماران پایگاه داده | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | مدیران شبکه و سیستم‌های کامپیوتری | متخصصان آزمون نفوذپذیری و ارزیابی امنیتی | کارشناسان مدیریت پروژه | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و آزمون‌گران تضمین کیفیت نرم‌افزار | متخصصان مهندسی مخابرات | طراحان وب و رابط‌های دیجیتال</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نگارش | شنیدن فعال | درک مطلب | سخن گفتن | نظارت | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | نگارش | گوش دادن فعال | درک مطلب | سخن گفتن | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | مدیریت و امور اداری | مهندسی و فناوری | اقتصاد و حسابداری | امور اداری | مخابرات و ارتباطات | ریاضیات | مدیریت منابع انسانی و امور پرسنلی | ارتباطات و رسانه</t>
+          <t>زبان انگلیسی | خدمات مشتری و شخصی | رایانه و الکترونیک | مدیریت و اداره | مهندسی و فناوری | اقتصاد و حسابداری | اداری | مخابرات | ریاضیات | پرسنل و منابع انسانی | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | درک شفاهی | روان بودن ایده‌ها | دید نزدیک | تشخیص گفتار | وضوح گفتار | ابتکار و اصالت | انعطاف‌پذیری در طبقه‌بندی | تسلط بر کار با اعداد | وضوح گفتار | استدلال ریاضی</t>
+          <t>درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | درک شفاهی | روانی ایده‌ها | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | اصالت | انعطاف‌پذیری دسته‌بندی | توانایی عددی | انعطاف‌پذیری بستار | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | مدیران معماری و مهندسی | برنامه‌ریزان تداوم کسب‌وکار | تحلیل‌گران سامانه‌های رایانه‌ای | مهندسان و معماران سامانه‌های رایانه‌ای | مدیران فناوری اطلاعات و سامانه‌های رایانه‌ای | مدیران پایگاه داده | مهندسان معمار پایگاه داده | کارشناسان مدیریت اسناد و مدارک | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | مدیران ارشد و مدیران عملیات | مهندسان صنایع | مهندسان لجستیک | تحلیل‌گران مدیریت | راهبران شبکه و سامانه‌های رایانه‌ای | تحلیل‌گران تحقیق در عملیات | کارشناسان مدیریت پروژه | توسعه‌دهندگان نرم‌افزار | مدیران نصب تأسیسات انرژی خورشیدی | مدیران پایگاه‌های اینترنتی</t>
+          <t>مدیران خدمات اداری و پشتیبانی | مدیران فنی و مهندسی و معماری | کارشناسان برنامه‌ریزی تداوم کسب‌وکار | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | مدیران فناوری اطلاعات و سیستم‌های رایانه‌ای | مدیران پایگاه داده | معماران پایگاه داده | کارشناسان مدیریت اسناد و مدارک | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | مدیران کل و مدیران عملیات | مهندسان صنایع | مهندسان لجستیک و زنجیره تأمین | کارشناسان تحلیل مدیریت و روش‌ها | مدیران شبکه و سیستم‌های کامپیوتری | تحلیل‌گران تحقیق در عملیات | کارشناسان مدیریت پروژه | توسعه‌دهندگان نرم‌افزار | مدیران اجرای پروژه‌های انرژی خورشیدی | مدیران وب</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | ریاضیات | درک مطلب | شنیدن فعال | سخن گفتن | نگارش | یادگیری فعال | نظارت</t>
+          <t>تفکر انتقادی | ریاضیات | درک مطلب | گوش دادن فعال | سخن گفتن | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ریاضیات | رایانه و الکترونیک | اقتصاد و حسابداری | زبان انگلیسی | امور حقوقی و دولتی</t>
+          <t>ریاضیات | رایانه و الکترونیک | اقتصاد و حسابداری | زبان انگلیسی | قانون و دولت</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>استدلال ریاضی | استدلال استقرایی | تسلط بر کار با اعداد | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | انعطاف‌پذیری در طبقه‌بندی | بیان شفاهی | حساسیت به مسئله | مرتب‌سازی اطلاعات | دید نزدیک | وضوح گفتار | تشخیص گفتار | وضوح گفتار | توجه انتخابی | روان بودن ایده‌ها</t>
+          <t>استدلال ریاضی | استدلال استقرایی | توانایی عددی | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | بیان شفاهی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری بستار | توجه انتخابی | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | تحلیل‌گران هوش تجاری | مدیران جبران خدمت و مزایا | کارشناسان ارزیابی شغل، جبران خدمت و مزایا | تحلیل‌گران اعتباری | اقتصاددانان | کارشناسان ممیزی و ارزیابی مالی | مدیران مالی | تحلیل‌گران محاسبات مالی | کارشناسان ریسک مالی | تحلیل‌گران مالی و سرمایه‌گذاری | نمایندگان فروش بیمه | کارشناسان صدور بیمه‌نامه (ارزیابان ریسک) | مدیران صندوق‌های سرمایه‌گذاری | تحلیل‌گران مدیریت | مشاوران مالی شخصی | کارشناسان فروش خدمات | نمایندگان فروش اوراق بهادار، کالا و خدمات مالی | دستیاران آمار | آمارشناسان</t>
+          <t>حسابداران و حسابرسان | تحلیل‌گران هوش تجاری | مدیران جبران خدمت و مزایا | کارشناسان جبران خدمت، مزایا و طبقه‌بندی مشاغل | تحلیل‌گران اعتبارات و تسهیلات | اقتصاددانان | بازرسان و ارزیابان مالی | مدیران امور مالی | تحلیل‌گران کمّی مالی | کارشناسان ریسک مالی | تحلیل‌گران مالی و سرمایه‌گذاری | نمایندگان و کارشناسان فروش بیمه | کارشناسان صدور بیمه‌نامه و ارزیابی ریسک | مدیران صندوق‌های سرمایه‌گذاری | کارشناسان تحلیل مدیریت و روش‌ها | مشاوران مالی فردی | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | کارشناسان فروش اوراق بهادار، کالاها و خدمات مالی | دستیاران و تکنسین‌های آمار | کارشناسان آمار</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ریاضیات | تفکر انتقادی | درک مطلب | یادگیری فعال | علوم پایه | نگارش | شنیدن فعال | استراتژی‌های یادگیری | سخن گفتن | نظارت</t>
+          <t>ریاضیات | تفکر انتقادی | درک مطلب | یادگیری فعال | علوم | نگارش | گوش دادن فعال | راهبردهای یادگیری | سخن گفتن | نظارت</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ریاضیات | آموزش و تدریس | رایانه و الکترونیک | زبان انگلیسی | فیزیک</t>
+          <t>ریاضیات | آموزش و پرورش | رایانه و الکترونیک | زبان انگلیسی | فیزیک</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>استدلال ریاضی | تسلط بر کار با اعداد | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | انعطاف‌پذیری در طبقه‌بندی | روان بودن ایده‌ها | ابتکار و اصالت | حساسیت به مسئله | دید نزدیک | وضوح گفتار | توجه انتخابی | وضوح گفتار | تشخیص گفتار</t>
+          <t>استدلال ریاضی | توانایی عددی | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | حساسیت به مسئله | بینایی نزدیک | انعطاف‌پذیری بستار | توجه انتخابی | وضوح گفتار | تشخیص گفتار</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ستاره‌شناسان | زیست‌شیمی‌دانان و زیست‌فیزیک‌دانان | مهندسان زیستی و مهندسان پزشکی | دانشمندان بیوانفورماتیک | تکنسین‌های بیوانفورماتیک | متخصصان آمار زیستی | دانشمندان پژوهش‌های رایانه و اطلاعات | دانشمندان داده | تحلیل‌گران محاسبات مالی | متخصصان ژنتیک | دانشمندان علوم زمین (زمین‌شناسان) | استادان و مدرسان علوم ریاضی در دانشگاه | زیست‌شناسان مولکولی و سلولی | مهندسان نانوسیستم | تحلیل‌گران تحقیق در عملیات | فیزیک‌دانان | استادان و مدرسان فیزیک در دانشگاه | توسعه‌دهندگان نرم‌افزار | دستیاران آمار | آمارشناسان</t>
+          <t>ستاره‌شناسان و اخترشناسان | زیست‌شیمی‌دانان و زیست‌فیزیک‌دانان | مهندسان پزشکی و بیوانجینیرینگ | متخصصان بیوانفورماتیک | تکنسین‌های بیوانفورماتیک | کارشناسان آمار زیستی | پژوهشگران علوم رایانه و اطلاعات | دانشمندان داده | تحلیل‌گران کمّی مالی | متخصصان ژنتیک | زمین‌شناسان به استثنای آب‌زمین‌شناسان و جغرافیدانان | استادان و مدرسان علوم ریاضی در دانشگاه‌ها و مراکز آموزش عالی | زیست‌شناسان سلولی و مولکولی | مهندسان نانوسیستم‌ها | تحلیل‌گران تحقیق در عملیات | فیزیک‌دانان | استادان و مدرسان فیزیک در دانشگاه‌ها و مراکز آموزش عالی | توسعه‌دهندگان نرم‌افزار | دستیاران و تکنسین‌های آمار | کارشناسان آمار</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ریاضیات | نگارش | تفکر انتقادی | سخن گفتن | شنیدن فعال | درک مطلب | یادگیری فعال | علوم پایه | استراتژی‌های یادگیری</t>
+          <t>ریاضیات | نگارش | تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | یادگیری فعال | علوم | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ریاضیات | رایانه و الکترونیک | مهندسی و فناوری | تولید و فراوری | زبان انگلیسی | طراحی | آموزش و تدریس</t>
+          <t>ریاضیات | رایانه و الکترونیک | مهندسی و فناوری | تولید و فرآوری | زبان انگلیسی | طراحی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>استدلال ریاضی | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | تسلط بر کار با اعداد | مرتب‌سازی اطلاعات | دید نزدیک | روان بودن ایده‌ها | ابتکار و اصالت | انعطاف‌پذیری در طبقه‌بندی | وضوح گفتار | تشخیص گفتار | وضوح گفتار | توجه انتخابی</t>
+          <t>استدلال ریاضی | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | توانایی عددی | ترتیب‌دهی اطلاعات | بینایی نزدیک | روانی ایده‌ها | اصالت | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری بستار | توجه انتخابی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>تحلیل‌گران هوش تجاری | تحلیل‌گران سامانه‌های رایانه‌ای | مهندسان و معماران سامانه‌های رایانه‌ای | دانشمندان پژوهش‌های رایانه و اطلاعات | دانشمندان داده | کارشناسان پایگاه داده و انبار داده | مدیران پایگاه داده | مهندسان معمار پایگاه داده | تحلیل‌گران محاسبات مالی | کارشناسان ریسک مالی | متخصصان فناوری اطلاعات سلامت و ثبت اطلاعات پزشکی | مهندسان صنایع | مهندسان لجستیک | تحلیل‌گران مدیریت | ریاضی‌دانان | کارشناسان مدیریت پروژه | توسعه‌دهندگان نرم‌افزار | کارشناسان تضمین کیفیت و آزمون نرم‌افزار | دستیاران آمار | آمارشناسان</t>
+          <t>تحلیل‌گران هوش تجاری | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | پژوهشگران علوم رایانه و اطلاعات | دانشمندان داده | متخصصان انباره داده | مدیران پایگاه داده | معماران پایگاه داده | تحلیل‌گران کمّی مالی | کارشناسان ریسک مالی | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | مهندسان صنایع | مهندسان لجستیک و زنجیره تأمین | کارشناسان تحلیل مدیریت و روش‌ها | ریاضی‌دانان | کارشناسان مدیریت پروژه | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و آزمون‌گران تضمین کیفیت نرم‌افزار | دستیاران و تکنسین‌های آمار | کارشناسان آمار</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
